--- a/output/yearly_surface_area_iteration_77_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_77_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497615497264</v>
+        <v>10.84497630162837</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907132431235</v>
+        <v>37.78907183533087</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.164393834965722</v>
+        <v>6.14966761940202</v>
       </c>
       <c r="C2" t="n">
-        <v>7.745989386507333</v>
+        <v>5.821763886183585</v>
       </c>
       <c r="D2" t="n">
-        <v>22.92086365105028</v>
+        <v>23.40977400776519</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.07674055184727</v>
+        <v>20.00310947402876</v>
       </c>
       <c r="C3" t="n">
-        <v>34.80786485407066</v>
+        <v>31.80862561759665</v>
       </c>
       <c r="D3" t="n">
-        <v>52.70021676396878</v>
+        <v>68.98741117742337</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.65377152223292</v>
+        <v>41.90001026954963</v>
       </c>
       <c r="C4" t="n">
-        <v>67.83385762493337</v>
+        <v>75.68293052038661</v>
       </c>
       <c r="D4" t="n">
-        <v>71.01177494358029</v>
+        <v>97.11153766098174</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.08109381548755</v>
+        <v>49.30827844579606</v>
       </c>
       <c r="C5" t="n">
-        <v>90.46805094634358</v>
+        <v>104.8751985061655</v>
       </c>
       <c r="D5" t="n">
-        <v>58.07037670619884</v>
+        <v>77.11628216858696</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.70071548558752</v>
+        <v>46.12839763174064</v>
       </c>
       <c r="C6" t="n">
-        <v>108.5989675483737</v>
+        <v>110.4505437185832</v>
       </c>
       <c r="D6" t="n">
-        <v>44.92084795551706</v>
+        <v>52.08564270111029</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.24840753137022</v>
+        <v>33.17718191731671</v>
       </c>
       <c r="C7" t="n">
-        <v>93.06379187637214</v>
+        <v>78.63111887623978</v>
       </c>
       <c r="D7" t="n">
-        <v>39.16584291322225</v>
+        <v>41.08221443191203</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.35315143608837</v>
+        <v>17.60764507566654</v>
       </c>
       <c r="C8" t="n">
-        <v>65.00642423670254</v>
+        <v>45.47946239923349</v>
       </c>
       <c r="D8" t="n">
-        <v>36.55046702910875</v>
+        <v>36.38356991938679</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.432811868852599</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>40.82499653339935</v>
+        <v>30.17499743772996</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>29.18245050873644</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>34.59188035913637</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>28.42257778564941</v>
+        <v>27.98864530037232</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>26.27647730416588</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1010,7 +1010,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.712984829833423</v>
+        <v>7.695513820388009</v>
       </c>
       <c r="C21" t="n">
-        <v>95.44818726918861</v>
+        <v>94.27004429975311</v>
       </c>
       <c r="D21" t="n">
-        <v>8.677107933562601</v>
+        <v>8.65745304793651</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.942919764433443</v>
+        <v>8.537278036130262</v>
       </c>
       <c r="C2" t="n">
-        <v>11.61014835042278</v>
+        <v>6.858489461868218</v>
       </c>
       <c r="D2" t="n">
-        <v>22.54190903721101</v>
+        <v>21.66226309420587</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.35162990903638</v>
+        <v>20.21418523044183</v>
       </c>
       <c r="C3" t="n">
-        <v>32.48112279500572</v>
+        <v>26.90970457340507</v>
       </c>
       <c r="D3" t="n">
-        <v>57.57459411555419</v>
+        <v>70.88709298514094</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.70933023074748</v>
+        <v>39.66653424238812</v>
       </c>
       <c r="C4" t="n">
-        <v>76.8571007746658</v>
+        <v>76.74223629326892</v>
       </c>
       <c r="D4" t="n">
-        <v>78.93742415996479</v>
+        <v>106.6452896169225</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.92249265575607</v>
+        <v>55.93507544946203</v>
       </c>
       <c r="C5" t="n">
-        <v>107.7713542336936</v>
+        <v>121.810346404423</v>
       </c>
       <c r="D5" t="n">
-        <v>69.0904946863693</v>
+        <v>92.65243958829274</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.60891422747383</v>
+        <v>55.54728510628455</v>
       </c>
       <c r="C6" t="n">
-        <v>124.7398815538955</v>
+        <v>136.050596854523</v>
       </c>
       <c r="D6" t="n">
-        <v>51.60262283062086</v>
+        <v>62.26931163726245</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.20765715387736</v>
+        <v>43.35790561035613</v>
       </c>
       <c r="C7" t="n">
-        <v>124.5641487148353</v>
+        <v>117.1980956898715</v>
       </c>
       <c r="D7" t="n">
-        <v>43.05847256056086</v>
+        <v>46.35223610830891</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.44627859927157</v>
+        <v>26.36974333606933</v>
       </c>
       <c r="C8" t="n">
-        <v>92.79479300540851</v>
+        <v>72.60024272905163</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>38.7201294554942</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>12.64687392610741</v>
       </c>
       <c r="C9" t="n">
-        <v>60.4609323660398</v>
+        <v>42.82187136383736</v>
       </c>
       <c r="D9" t="n">
-        <v>35.83280945730432</v>
+        <v>35.94374694788421</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>39.43189654107314</v>
+        <v>32.59893251951534</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1220,7 +1220,7 @@
         <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>31.02617269731195</v>
+        <v>30.59224021203486</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>29.13827186204534</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.900311286632307</v>
+        <v>7.878114933077453</v>
       </c>
       <c r="C21" t="n">
-        <v>104.6791245478781</v>
+        <v>103.4002584966416</v>
       </c>
       <c r="D21" t="n">
-        <v>9.875389108290383</v>
+        <v>9.847643666346816</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.315803965597985</v>
+        <v>9.584802836561609</v>
       </c>
       <c r="C2" t="n">
-        <v>9.464047868939252</v>
+        <v>7.384706231344508</v>
       </c>
       <c r="D2" t="n">
-        <v>19.84897508446201</v>
+        <v>24.63990388118645</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.4070086911017</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="C3" t="n">
-        <v>38.35197406640165</v>
+        <v>26.56609287691869</v>
       </c>
       <c r="D3" t="n">
-        <v>60.85363144773854</v>
+        <v>71.0245376637355</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.02014334236623</v>
+        <v>38.30092318578082</v>
       </c>
       <c r="C4" t="n">
-        <v>77.94193198785852</v>
+        <v>71.40741926839175</v>
       </c>
       <c r="D4" t="n">
-        <v>86.64610713371074</v>
+        <v>115.3239393224643</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.4687452899448</v>
+        <v>57.11317269455821</v>
       </c>
       <c r="C5" t="n">
-        <v>123.1847931903686</v>
+        <v>130.4006388165826</v>
       </c>
       <c r="D5" t="n">
-        <v>79.69336989223484</v>
+        <v>105.1206354322272</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>61.82654342264714</v>
+        <v>63.83912621635311</v>
       </c>
       <c r="C6" t="n">
-        <v>144.3021863087175</v>
+        <v>159.7588221643792</v>
       </c>
       <c r="D6" t="n">
-        <v>59.29068910257763</v>
+        <v>74.34480839949822</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>48.56804067679396</v>
+        <v>53.11942303368217</v>
       </c>
       <c r="C7" t="n">
-        <v>150.195617777311</v>
+        <v>151.0340303167378</v>
       </c>
       <c r="D7" t="n">
-        <v>47.54996830749001</v>
+        <v>51.74203100462389</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.95803119509142</v>
+        <v>35.549084370777</v>
       </c>
       <c r="C8" t="n">
-        <v>124.2548981879975</v>
+        <v>108.9838126484384</v>
       </c>
       <c r="D8" t="n">
-        <v>40.55599766243574</v>
+        <v>41.80772598535042</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.42031119060464</v>
+        <v>18.41562343626167</v>
       </c>
       <c r="C9" t="n">
-        <v>84.42343033129593</v>
+        <v>62.90155715879737</v>
       </c>
       <c r="D9" t="n">
-        <v>37.49687181600267</v>
+        <v>37.16405934426299</v>
       </c>
     </row>
     <row r="10">
@@ -1514,10 +1514,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.114144775599888</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>53.95194508688347</v>
+        <v>40.85543071223102</v>
       </c>
       <c r="D10" t="n">
         <v>36.44247478164161</v>
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>5.508586368528851</v>
       </c>
       <c r="C11" t="n">
-        <v>38.56010457970196</v>
+        <v>34.82848155585983</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>31.47974013667398</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="D13" t="n">
-        <v>33.82120841130262</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>28.5776939229204</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>31.65056423721292</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>27.69215749368978</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>20.30548776693678</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>19.25796296650543</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.071768166952598</v>
+        <v>8.045332030541344</v>
       </c>
       <c r="C21" t="n">
-        <v>113.0047543373364</v>
+        <v>111.6289819237612</v>
       </c>
       <c r="D21" t="n">
-        <v>11.09868122955982</v>
+        <v>11.06233154199435</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.33798325216816</v>
+        <v>8.685521939471531</v>
       </c>
       <c r="C2" t="n">
-        <v>6.359761628110838</v>
+        <v>5.020657759518188</v>
       </c>
       <c r="D2" t="n">
-        <v>16.18705614762141</v>
+        <v>20.25738212942869</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.31574721233575</v>
+        <v>27.66074156715388</v>
       </c>
       <c r="C3" t="n">
-        <v>54.67352964950487</v>
+        <v>41.00760160638927</v>
       </c>
       <c r="D3" t="n">
-        <v>66.79320505843174</v>
+        <v>78.65271732573322</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.64855968407542</v>
+        <v>27.43984833369835</v>
       </c>
       <c r="C4" t="n">
-        <v>105.637034724661</v>
+        <v>104.8457460750381</v>
       </c>
       <c r="D4" t="n">
-        <v>85.63785224144928</v>
+        <v>114.1625317883403</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.82749980815561</v>
+        <v>35.95650966803944</v>
       </c>
       <c r="C5" t="n">
-        <v>86.22199212547613</v>
+        <v>95.45042054539616</v>
       </c>
       <c r="D5" t="n">
-        <v>57.60404654668161</v>
+        <v>72.67387380687015</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.14849024971531</v>
+        <v>32.96610616090365</v>
       </c>
       <c r="C6" t="n">
-        <v>98.89831848271095</v>
+        <v>99.46184166494862</v>
       </c>
       <c r="D6" t="n">
-        <v>31.31578827006476</v>
+        <v>34.05290086950487</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.82246789644735</v>
+        <v>23.53543771390878</v>
       </c>
       <c r="C7" t="n">
-        <v>87.37456393026187</v>
+        <v>76.59497413763189</v>
       </c>
       <c r="D7" t="n">
-        <v>28.50602634051038</v>
+        <v>29.34443887993716</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>12.76762889372977</v>
       </c>
       <c r="C8" t="n">
-        <v>62.16917337142927</v>
+        <v>46.31394794784328</v>
       </c>
       <c r="D8" t="n">
-        <v>27.62147165898401</v>
+        <v>27.37112599440107</v>
       </c>
     </row>
     <row r="9">
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>6.434374453633594</v>
       </c>
       <c r="C9" t="n">
-        <v>41.15780900513902</v>
+        <v>31.17343485294896</v>
       </c>
       <c r="D9" t="n">
         <v>27.73437264497238</v>
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>29.04009709162065</v>
+        <v>28.61303684027329</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.60910984945629</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>27.55471281509523</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.58662746324986</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>74.64718669240621</v>
       </c>
       <c r="D20" t="n">
         <v>7.397468951499714</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.948990177108171</v>
+        <v>5.228788272818512</v>
       </c>
       <c r="C2" t="n">
-        <v>2.684098223410779</v>
+        <v>2.852958828541231</v>
       </c>
       <c r="D2" t="n">
-        <v>11.15363566794801</v>
+        <v>14.59171612822034</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.24488145118073</v>
+        <v>29.56042337487146</v>
       </c>
       <c r="C3" t="n">
-        <v>39.72151211382595</v>
+        <v>30.5176273865121</v>
       </c>
       <c r="D3" t="n">
-        <v>65.51202430438966</v>
+        <v>77.19973072344794</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.20332925243288</v>
+        <v>38.73485567105791</v>
       </c>
       <c r="C4" t="n">
-        <v>125.0108439202676</v>
+        <v>106.5176624153704</v>
       </c>
       <c r="D4" t="n">
-        <v>98.19636887417447</v>
+        <v>126.746573861376</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.02447124381072</v>
+        <v>40.25165587411923</v>
       </c>
       <c r="C5" t="n">
-        <v>137.9355524466769</v>
+        <v>142.8933783531233</v>
       </c>
       <c r="D5" t="n">
-        <v>70.31767931667781</v>
+        <v>90.17352663506955</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.46800022195202</v>
+        <v>39.68813269188156</v>
       </c>
       <c r="C6" t="n">
-        <v>119.0241464197706</v>
+        <v>125.7461729507485</v>
       </c>
       <c r="D6" t="n">
-        <v>37.91705983342032</v>
+        <v>42.78751019418875</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.80439552714341</v>
+        <v>22.09815907489146</v>
       </c>
       <c r="C7" t="n">
-        <v>111.9879606234337</v>
+        <v>102.1066699801895</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.095892479846697</v>
+        <v>10.59796646734432</v>
       </c>
       <c r="C8" t="n">
-        <v>81.11199532487147</v>
+        <v>64.00504157837081</v>
       </c>
       <c r="D8" t="n">
-        <v>28.62285431731576</v>
+        <v>28.53940576245478</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>48.14687091167205</v>
+        <v>36.38749691020377</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>28.6218725696115</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2153,7 +2153,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>30.56376952861169</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
         <v>29.67528785626833</v>
@@ -2167,10 +2167,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69185439405351</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>64.99562501195582</v>
       </c>
       <c r="D19" t="n">
         <v>6.018113427032947</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.723188205131405</v>
+        <v>5.974916528046087</v>
       </c>
       <c r="C2" t="n">
-        <v>10.16992446829271</v>
+        <v>7.856926877087224</v>
       </c>
       <c r="D2" t="n">
-        <v>15.76981337331651</v>
+        <v>16.467835991036</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.42311756499715</v>
+        <v>23.59630607157209</v>
       </c>
       <c r="C3" t="n">
-        <v>23.99391389179205</v>
+        <v>20.10619298297468</v>
       </c>
       <c r="D3" t="n">
-        <v>59.59699438630262</v>
+        <v>71.27488332831844</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.92026711844031</v>
+        <v>47.29864089520283</v>
       </c>
       <c r="C4" t="n">
-        <v>111.5589368766778</v>
+        <v>90.73017758337748</v>
       </c>
       <c r="D4" t="n">
-        <v>107.6663072293392</v>
+        <v>135.6677152498667</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.09934611124073</v>
+        <v>48.81740459367266</v>
       </c>
       <c r="C5" t="n">
-        <v>184.2495003945202</v>
+        <v>171.0204500797944</v>
       </c>
       <c r="D5" t="n">
-        <v>87.49826414099698</v>
+        <v>112.4837432140783</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.43782808502763</v>
+        <v>47.13468902859362</v>
       </c>
       <c r="C6" t="n">
-        <v>168.3726765214408</v>
+        <v>173.4846368174539</v>
       </c>
       <c r="D6" t="n">
-        <v>49.26802678992194</v>
+        <v>58.32464936159877</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.68568617038755</v>
+        <v>32.45854259780804</v>
       </c>
       <c r="C7" t="n">
-        <v>141.6917191631251</v>
+        <v>140.4939869639441</v>
       </c>
       <c r="D7" t="n">
-        <v>34.49468733641593</v>
+        <v>36.77037851486003</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.51866588747858</v>
+        <v>15.52143120414207</v>
       </c>
       <c r="C8" t="n">
-        <v>112.6555490623215</v>
+        <v>96.80032363873549</v>
       </c>
       <c r="D8" t="n">
-        <v>30.62561963397925</v>
+        <v>30.29182541453534</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.212499472473814</v>
+        <v>6.878124415953151</v>
       </c>
       <c r="C9" t="n">
-        <v>71.33280644286897</v>
+        <v>55.24687030878498</v>
       </c>
       <c r="D9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.39843500367073</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>2.847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>43.84485247166256</v>
+        <v>36.86953503298896</v>
       </c>
       <c r="D10" t="n">
-        <v>30.89069151412589</v>
+        <v>30.60598467989432</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>34.47308888692249</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
         <v>30.20837685967435</v>
@@ -2478,10 +2478,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>26.68684784454105</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.07347651356504</v>
       </c>
     </row>
     <row r="13">
@@ -2495,7 +2495,7 @@
         <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>20.28094407433061</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
         <v>11.33329549782518</v>
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.783254741539707</v>
+        <v>3.514656781203581</v>
       </c>
       <c r="C2" t="n">
-        <v>4.664283342876596</v>
+        <v>3.606941065402781</v>
       </c>
       <c r="D2" t="n">
-        <v>10.87187407682918</v>
+        <v>11.36274792895258</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.09423208407447</v>
+        <v>24.45533531278805</v>
       </c>
       <c r="C3" t="n">
-        <v>32.46148784092079</v>
+        <v>26.05558407071035</v>
       </c>
       <c r="D3" t="n">
-        <v>60.31857894892403</v>
+        <v>70.79873569175872</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.37445645260809</v>
+        <v>52.30162719604458</v>
       </c>
       <c r="C4" t="n">
-        <v>103.4163214176548</v>
+        <v>84.62959734918779</v>
       </c>
       <c r="D4" t="n">
-        <v>114.5326506728414</v>
+        <v>143.3763982236127</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.01375413452202</v>
+        <v>50.6827252317416</v>
       </c>
       <c r="C5" t="n">
-        <v>218.6597574283709</v>
+        <v>198.0185119465817</v>
       </c>
       <c r="D5" t="n">
-        <v>94.34595437811849</v>
+        <v>120.7549676223577</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.26674194258143</v>
+        <v>39.72838434775569</v>
       </c>
       <c r="C6" t="n">
-        <v>203.0696038849315</v>
+        <v>207.2557760958399</v>
       </c>
       <c r="D6" t="n">
-        <v>48.42274201656544</v>
+        <v>56.67433147075987</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.92310488389926</v>
+        <v>10.24061030299848</v>
       </c>
       <c r="C7" t="n">
-        <v>149.6566382876795</v>
+        <v>139.8951208643535</v>
       </c>
       <c r="D7" t="n">
-        <v>34.91389360612931</v>
+        <v>36.53083207502382</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>87.87132826861075</v>
+        <v>71.01472018669303</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>33.39218466454675</v>
+        <v>28.06718511671205</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
         <v>23.63066724122073</v>
@@ -2775,10 +2775,10 @@
         <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>21.32356013624072</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.27821981539612</v>
       </c>
     </row>
     <row r="12">
@@ -2792,7 +2792,7 @@
         <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
         <v>9.506263020221864</v>
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.57396255408589</v>
+        <v>4.085052197370977</v>
       </c>
       <c r="C2" t="n">
-        <v>8.472482687649974</v>
+        <v>4.030074325933156</v>
       </c>
       <c r="D2" t="n">
-        <v>15.00208666859551</v>
+        <v>13.32427984203771</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.96812640957437</v>
+        <v>18.40286071610646</v>
       </c>
       <c r="C3" t="n">
-        <v>25.09347132054847</v>
+        <v>19.86075605691298</v>
       </c>
       <c r="D3" t="n">
-        <v>55.45401907438109</v>
+        <v>64.13757751844412</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.04338649209866</v>
+        <v>50.18301565027996</v>
       </c>
       <c r="C4" t="n">
-        <v>93.12956897255668</v>
+        <v>75.56806603898974</v>
       </c>
       <c r="D4" t="n">
-        <v>117.9530596744373</v>
+        <v>145.6481624112398</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.50020227420971</v>
+        <v>62.68459091615885</v>
       </c>
       <c r="C5" t="n">
-        <v>205.1852701875834</v>
+        <v>179.8807231106219</v>
       </c>
       <c r="D5" t="n">
-        <v>111.722888743287</v>
+        <v>142.0343491119073</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.85921883432777</v>
+        <v>50.99884799250906</v>
       </c>
       <c r="C6" t="n">
-        <v>272.3024519884166</v>
+        <v>257.0068227562513</v>
       </c>
       <c r="D6" t="n">
-        <v>62.06805335789186</v>
+        <v>74.90833158173589</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.36144738607885</v>
+        <v>22.63713856452295</v>
       </c>
       <c r="C7" t="n">
-        <v>212.2980323048515</v>
+        <v>208.8844955371853</v>
       </c>
       <c r="D7" t="n">
-        <v>39.58504918293564</v>
+        <v>42.57937968088841</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>6.592435834017332</v>
       </c>
       <c r="C8" t="n">
-        <v>135.3535559845078</v>
+        <v>119.1645363414778</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>33.71321616383547</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>60.90468232835936</v>
+        <v>50.25468323268996</v>
       </c>
       <c r="D9" t="n">
-        <v>33.61405964570653</v>
+        <v>33.28124717396686</v>
       </c>
     </row>
     <row r="10">
@@ -3072,7 +3072,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
         <v>24.76949457814703</v>
@@ -3086,10 +3086,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>25.05518316008284</v>
+        <v>24.16670148773948</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3103,7 +3103,7 @@
         <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3131,7 +3131,7 @@
         <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>24.38563122578652</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>34.47210713921825</v>
       </c>
       <c r="D17" t="n">
         <v>4.722206457427158</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.030655163009904</v>
+        <v>2.96095107600838</v>
       </c>
       <c r="C2" t="n">
-        <v>4.020256848890688</v>
+        <v>2.654645792283375</v>
       </c>
       <c r="D2" t="n">
-        <v>10.59992996275281</v>
+        <v>9.824349276397832</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.9730351480956</v>
+        <v>16.69952844923824</v>
       </c>
       <c r="C3" t="n">
-        <v>28.98119222936585</v>
+        <v>18.11815388187489</v>
       </c>
       <c r="D3" t="n">
-        <v>54.78152189697202</v>
+        <v>60.94198874112075</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.82343394861837</v>
+        <v>45.55014823393926</v>
       </c>
       <c r="C4" t="n">
-        <v>82.35783316156066</v>
+        <v>66.28956848615313</v>
       </c>
       <c r="D4" t="n">
-        <v>119.0123654473196</v>
+        <v>145.4439588887565</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>66.34160111447822</v>
+        <v>69.28684422721865</v>
       </c>
       <c r="C5" t="n">
-        <v>199.2702402694964</v>
+        <v>170.4314014572463</v>
       </c>
       <c r="D5" t="n">
-        <v>123.7247544277043</v>
+        <v>156.3433219013046</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.67433147075987</v>
+        <v>59.97496725243766</v>
       </c>
       <c r="C6" t="n">
-        <v>303.497485290859</v>
+        <v>279.5074983898839</v>
       </c>
       <c r="D6" t="n">
-        <v>72.97625209977816</v>
+        <v>89.11716610529999</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.92416874706152</v>
+        <v>21.25974653546468</v>
       </c>
       <c r="C7" t="n">
-        <v>273.9812405626786</v>
+        <v>263.560970429803</v>
       </c>
       <c r="D7" t="n">
-        <v>44.49575119957818</v>
+        <v>48.32849423695774</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>5.340707511102648</v>
       </c>
       <c r="C8" t="n">
-        <v>174.1571339948629</v>
+        <v>160.8888137719673</v>
       </c>
       <c r="D8" t="n">
-        <v>34.88149593188918</v>
+        <v>35.13184159647211</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>71.22186895228909</v>
+        <v>59.68436993198057</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>33.73775985644164</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
         <v>24.16670148773948</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>3.719842051391165</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.061891163096554</v>
+        <v>4.630903920932204</v>
       </c>
       <c r="C2" t="n">
-        <v>6.85161722793849</v>
+        <v>6.053456344385832</v>
       </c>
       <c r="D2" t="n">
-        <v>19.16960567312322</v>
+        <v>14.99914142548277</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.19468914507713</v>
+        <v>13.48430471782994</v>
       </c>
       <c r="C3" t="n">
-        <v>22.81581664669588</v>
+        <v>14.3433339590459</v>
       </c>
       <c r="D3" t="n">
-        <v>51.06069809787661</v>
+        <v>55.62091618410305</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.24612524079224</v>
+        <v>38.92629647338603</v>
       </c>
       <c r="C4" t="n">
-        <v>76.88262621497621</v>
+        <v>56.61542660850506</v>
       </c>
       <c r="D4" t="n">
-        <v>118.7571110442154</v>
+        <v>142.8914148577148</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>65.58074664368695</v>
+        <v>68.89414514551993</v>
       </c>
       <c r="C5" t="n">
-        <v>178.2362957060084</v>
+        <v>149.1520199676967</v>
       </c>
       <c r="D5" t="n">
-        <v>134.0821927075081</v>
+        <v>166.6516727958961</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>68.83033154474388</v>
+        <v>72.93600044390405</v>
       </c>
       <c r="C6" t="n">
-        <v>312.9968760771512</v>
+        <v>277.0923990374368</v>
       </c>
       <c r="D6" t="n">
-        <v>87.50709987033521</v>
+        <v>110.4102920627091</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.91389360612931</v>
+        <v>38.38731698375453</v>
       </c>
       <c r="C7" t="n">
-        <v>339.9762847375577</v>
+        <v>324.2261063183261</v>
       </c>
       <c r="D7" t="n">
-        <v>52.16123727433727</v>
+        <v>58.56910453995621</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>10.93176068678823</v>
       </c>
       <c r="C8" t="n">
-        <v>249.010487705161</v>
+        <v>233.5725050558799</v>
       </c>
       <c r="D8" t="n">
-        <v>37.63529824230147</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>123.0296770530975</v>
+        <v>111.6031155233689</v>
       </c>
       <c r="D9" t="n">
-        <v>34.61249706092553</v>
+        <v>34.50155957034565</v>
       </c>
     </row>
     <row r="10">
@@ -3691,10 +3691,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>51.53193699591508</v>
+        <v>45.12603322570465</v>
       </c>
       <c r="D10" t="n">
         <v>26.47773558353648</v>
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>17.43093048890212</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.809582003105124</v>
+        <v>6.849653732529996</v>
       </c>
       <c r="C2" t="n">
-        <v>6.58065486156637</v>
+        <v>2.956042337487146</v>
       </c>
       <c r="D2" t="n">
-        <v>9.549459919208724</v>
+        <v>19.18531363639117</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.61970378555799</v>
+        <v>3.315361997241479</v>
       </c>
       <c r="C2" t="n">
-        <v>3.945644023367931</v>
+        <v>3.43808046027233</v>
       </c>
       <c r="D2" t="n">
-        <v>14.10869625773091</v>
+        <v>11.03877118655113</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.98070920328033</v>
+        <v>18.24578108342697</v>
       </c>
       <c r="C3" t="n">
-        <v>27.16495897650924</v>
+        <v>19.27661617288612</v>
       </c>
       <c r="D3" t="n">
-        <v>58.21763886183585</v>
+        <v>61.8844665371977</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.71079500453725</v>
+        <v>52.99081408442584</v>
       </c>
       <c r="C4" t="n">
-        <v>108.5341721998934</v>
+        <v>82.1025787584565</v>
       </c>
       <c r="D4" t="n">
-        <v>122.7518424527957</v>
+        <v>147.5370449942107</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.59526757060561</v>
+        <v>43.0005494460103</v>
       </c>
       <c r="C5" t="n">
-        <v>265.9799967730672</v>
+        <v>228.1581664669588</v>
       </c>
       <c r="D5" t="n">
-        <v>122.669375645639</v>
+        <v>154.5761760336603</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.65539086027615</v>
+        <v>23.82898027747859</v>
       </c>
       <c r="C6" t="n">
-        <v>285.263485179883</v>
+        <v>270.5716307858295</v>
       </c>
       <c r="D6" t="n">
-        <v>72.73474216453346</v>
+        <v>87.62785483795757</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.28809404570082</v>
+        <v>7.246279805045708</v>
       </c>
       <c r="C7" t="n">
-        <v>175.1084475202781</v>
+        <v>164.2689711176891</v>
       </c>
       <c r="D7" t="n">
-        <v>33.0574086973986</v>
+        <v>34.55457394637499</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>1.919316761802514</v>
       </c>
       <c r="C8" t="n">
-        <v>90.62513057902306</v>
+        <v>82.19682653806419</v>
       </c>
       <c r="D8" t="n">
-        <v>25.45180923259856</v>
+        <v>25.36836067773758</v>
       </c>
     </row>
     <row r="9">
@@ -4299,10 +4299,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
         <v>20.1906232855399</v>
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>23.20360698987336</v>
+        <v>22.06477965294707</v>
       </c>
       <c r="D10" t="n">
-        <v>19.3600647277471</v>
+        <v>19.07535789351553</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.70345544005523</v>
+        <v>16.52575910558656</v>
       </c>
       <c r="D11" t="n">
-        <v>16.70345544005523</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="D12" t="n">
-        <v>14.10280577150543</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.862997289761952</v>
+        <v>7.525096153051801</v>
       </c>
       <c r="C2" t="n">
-        <v>4.151811041259761</v>
+        <v>3.512693285795088</v>
       </c>
       <c r="D2" t="n">
-        <v>12.28460902324034</v>
+        <v>16.60822591274329</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.2199936012093</v>
+        <v>14.5445922384165</v>
       </c>
       <c r="C3" t="n">
-        <v>16.58171872472863</v>
+        <v>7.446556336712057</v>
       </c>
       <c r="D3" t="n">
-        <v>11.157562658765</v>
+        <v>19.25207248027995</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39840729534696</v>
+        <v>13.39702620451533</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14460289916937</v>
+        <v>70.1373724824626</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576283211217289</v>
+        <v>1.57612072994298</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.171445995344697</v>
+        <v>5.043237956715865</v>
       </c>
       <c r="C2" t="n">
-        <v>3.962333734340127</v>
+        <v>7.042076282562371</v>
       </c>
       <c r="D2" t="n">
-        <v>19.00663555421825</v>
+        <v>21.69269727303752</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.22338081267854</v>
+        <v>21.4217349066654</v>
       </c>
       <c r="C3" t="n">
-        <v>16.34119053718816</v>
+        <v>11.3588209381356</v>
       </c>
       <c r="D3" t="n">
-        <v>18.78083358224148</v>
+        <v>28.54922323949725</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.9714315055856</v>
+        <v>16.85955332503048</v>
       </c>
       <c r="C4" t="n">
-        <v>26.21462719879833</v>
+        <v>11.90761790480956</v>
       </c>
       <c r="D4" t="n">
-        <v>20.91809833438679</v>
+        <v>25.15532142591602</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>3.092505268377454</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.448699758569798</v>
       </c>
       <c r="D5" t="n">
         <v>29.10881943091793</v>
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.3139636433765</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4924,7 +4924,7 @@
         <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4938,7 +4938,7 @@
         <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>40.5049467818149</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44320614213367</v>
+        <v>15.44004136359705</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15683426664049</v>
+        <v>86.13917813375195</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251201293080773</v>
+        <v>3.250535023915168</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.104507225006667</v>
+        <v>5.122759520759856</v>
       </c>
       <c r="C2" t="n">
-        <v>6.587527095496098</v>
+        <v>6.10352547730242</v>
       </c>
       <c r="D2" t="n">
-        <v>18.87213611873644</v>
+        <v>24.8234907018806</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.2219981543468</v>
+        <v>19.18825887950391</v>
       </c>
       <c r="C3" t="n">
-        <v>15.78159434576748</v>
+        <v>21.08794068722149</v>
       </c>
       <c r="D3" t="n">
-        <v>29.6242369756475</v>
+        <v>39.27972564691488</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.90908267859932</v>
+        <v>30.71986741358695</v>
       </c>
       <c r="C4" t="n">
-        <v>34.88051418418493</v>
+        <v>21.63281066307847</v>
       </c>
       <c r="D4" t="n">
-        <v>25.64030479181395</v>
+        <v>33.80844569114741</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.92194320974577</v>
+        <v>14.79984664152067</v>
       </c>
       <c r="C5" t="n">
-        <v>29.84513020910304</v>
+        <v>14.87347771933918</v>
       </c>
       <c r="D5" t="n">
-        <v>29.96784867213389</v>
+        <v>31.44047022850411</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.15600007398401</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.8302651248191</v>
       </c>
     </row>
     <row r="7">
@@ -5207,10 +5207,10 @@
         <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.24947139453248</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.79113408536946</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5291,10 +5291,10 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>45.52854978444583</v>
       </c>
     </row>
     <row r="14">
@@ -5305,10 +5305,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5322,7 +5322,7 @@
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5347,7 +5347,7 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>37.30543101367455</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74024143106425</v>
+        <v>16.73473489825746</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1154727294919</v>
+        <v>102.0818828793705</v>
       </c>
       <c r="D21" t="n">
-        <v>5.022072429319274</v>
+        <v>5.020420469477239</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.949391087735671</v>
+        <v>5.633268326968198</v>
       </c>
       <c r="C2" t="n">
-        <v>7.320892630568465</v>
+        <v>9.280461048245099</v>
       </c>
       <c r="D2" t="n">
-        <v>15.82577299245858</v>
+        <v>25.31141931089127</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.34886459237289</v>
+        <v>18.29486846863931</v>
       </c>
       <c r="C3" t="n">
-        <v>21.52972715413255</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D3" t="n">
-        <v>37.37513510067607</v>
+        <v>49.40645321622073</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.38054256081604</v>
+        <v>34.37000537797658</v>
       </c>
       <c r="C4" t="n">
-        <v>37.50963453615788</v>
+        <v>38.81143199198916</v>
       </c>
       <c r="D4" t="n">
-        <v>33.97436105316512</v>
+        <v>44.91201222617884</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.89926520155685</v>
+        <v>30.2869166760141</v>
       </c>
       <c r="C5" t="n">
-        <v>48.866491978885</v>
+        <v>28.66703296400687</v>
       </c>
       <c r="D5" t="n">
-        <v>32.56948008838794</v>
+        <v>36.59464567579986</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.38492721552276</v>
+        <v>12.96103319146639</v>
       </c>
       <c r="C6" t="n">
-        <v>30.63151012020474</v>
+        <v>18.23400011097601</v>
       </c>
       <c r="D6" t="n">
-        <v>38.27932473628739</v>
+        <v>38.84284791852506</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>39.40538935305847</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>31.79389940203295</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>40.22220344299182</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -5560,7 +5560,7 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>9.062513057902304</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>46.86470840992573</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>46.30903920932205</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07216802381753</v>
+        <v>18.06325375715697</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8993818696667</v>
+        <v>117.8412268919288</v>
       </c>
       <c r="D21" t="n">
-        <v>6.884635437644773</v>
+        <v>6.881239526535988</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.38077924052752</v>
+        <v>7.8795070742849</v>
       </c>
       <c r="C2" t="n">
-        <v>5.155157195000002</v>
+        <v>6.865361695797945</v>
       </c>
       <c r="D2" t="n">
-        <v>17.16193161793849</v>
+        <v>23.52365674145782</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.45547418150829</v>
+        <v>17.00387023755476</v>
       </c>
       <c r="C3" t="n">
-        <v>24.05281875404685</v>
+        <v>28.46577468463627</v>
       </c>
       <c r="D3" t="n">
-        <v>38.65631585471816</v>
+        <v>54.24156065963628</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.12604892123787</v>
+        <v>25.2701859073129</v>
       </c>
       <c r="C4" t="n">
-        <v>39.25812719742145</v>
+        <v>40.47058561216627</v>
       </c>
       <c r="D4" t="n">
-        <v>38.50512670826415</v>
+        <v>50.91049069912684</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.19316761802515</v>
+        <v>25.15728492132452</v>
       </c>
       <c r="C5" t="n">
-        <v>44.32590884674349</v>
+        <v>38.77903431774902</v>
       </c>
       <c r="D5" t="n">
-        <v>30.43417883165113</v>
+        <v>36.12831551628263</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.39121861237574</v>
+        <v>14.93336432929824</v>
       </c>
       <c r="C6" t="n">
-        <v>37.79630486579796</v>
+        <v>21.93715245139498</v>
       </c>
       <c r="D6" t="n">
-        <v>30.79251674370121</v>
+        <v>32.28182801104362</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.329908286355933</v>
+        <v>6.048547605864599</v>
       </c>
       <c r="C7" t="n">
-        <v>21.31963314542373</v>
+        <v>15.39085875947725</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.18749811597791</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>29.84218496599028</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
         <v>33.73775985644164</v>
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
         <v>17.65673246087889</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.066592143437275</v>
+        <v>7.061382619537042</v>
       </c>
       <c r="C21" t="n">
-        <v>66.24930134472446</v>
+        <v>66.20046205815977</v>
       </c>
       <c r="D21" t="n">
-        <v>5.299944107577956</v>
+        <v>5.296036964652782</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.553746762924207</v>
+        <v>6.33718143091316</v>
       </c>
       <c r="C2" t="n">
-        <v>9.806677817721388</v>
+        <v>9.789988106749192</v>
       </c>
       <c r="D2" t="n">
-        <v>18.93300447639974</v>
+        <v>24.64775786282042</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.78145547704723</v>
+        <v>23.51285751671111</v>
       </c>
       <c r="C3" t="n">
-        <v>21.48063976892021</v>
+        <v>27.41039590257095</v>
       </c>
       <c r="D3" t="n">
-        <v>44.04611075103315</v>
+        <v>61.31505286873454</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.33698580893068</v>
+        <v>30.28593492830985</v>
       </c>
       <c r="C4" t="n">
-        <v>52.96528864411542</v>
+        <v>60.22727641242908</v>
       </c>
       <c r="D4" t="n">
-        <v>50.42550733322892</v>
+        <v>68.39541731176254</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.37250865273283</v>
+        <v>33.13398501832986</v>
       </c>
       <c r="C5" t="n">
-        <v>62.24280444924779</v>
+        <v>61.21196935978864</v>
       </c>
       <c r="D5" t="n">
-        <v>37.99363615435157</v>
+        <v>47.46750150033328</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.16607959293373</v>
+        <v>26.20382797405162</v>
       </c>
       <c r="C6" t="n">
-        <v>57.72087452348698</v>
+        <v>45.64537776125121</v>
       </c>
       <c r="D6" t="n">
-        <v>34.17365583712723</v>
+        <v>36.66925850132262</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.24061030299848</v>
+        <v>12.81573453123786</v>
       </c>
       <c r="C7" t="n">
-        <v>41.44153409166636</v>
+        <v>25.15237618280328</v>
       </c>
       <c r="D7" t="n">
-        <v>33.65627479698915</v>
+        <v>33.83593462686632</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>24.70077223884975</v>
+        <v>20.11110172149591</v>
       </c>
       <c r="D8" t="n">
-        <v>31.87734795689393</v>
+        <v>32.21114217633784</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.06249736236907</v>
       </c>
     </row>
     <row r="10">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6227,7 +6227,7 @@
         <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6238,10 +6238,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6255,7 +6255,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
@@ -6325,7 +6325,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.294359040951963</v>
+        <v>7.285987180917035</v>
       </c>
       <c r="C21" t="n">
-        <v>76.59076992999562</v>
+        <v>75.59211700201425</v>
       </c>
       <c r="D21" t="n">
-        <v>6.382564160832968</v>
+        <v>6.375238783302406</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.683337459884785</v>
+        <v>5.148284961070273</v>
       </c>
       <c r="C2" t="n">
-        <v>9.547496423800231</v>
+        <v>7.804894248762142</v>
       </c>
       <c r="D2" t="n">
-        <v>19.23930976012474</v>
+        <v>22.41919057418016</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.80814259151115</v>
+        <v>22.88944772451438</v>
       </c>
       <c r="C3" t="n">
-        <v>31.78408192499048</v>
+        <v>33.88993075059989</v>
       </c>
       <c r="D3" t="n">
-        <v>48.9695754878309</v>
+        <v>66.80793127399544</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.40302494702248</v>
+        <v>38.93905919354124</v>
       </c>
       <c r="C4" t="n">
-        <v>53.01633952473625</v>
+        <v>64.64317758613123</v>
       </c>
       <c r="D4" t="n">
-        <v>60.712259778327</v>
+        <v>83.12359637087319</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.23907308041327</v>
+        <v>40.34983064454391</v>
       </c>
       <c r="C5" t="n">
-        <v>83.37492378316038</v>
+        <v>90.34533248331273</v>
       </c>
       <c r="D5" t="n">
-        <v>48.15472489330606</v>
+        <v>62.14462967882311</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.26924521733767</v>
+        <v>36.38749691020379</v>
       </c>
       <c r="C6" t="n">
-        <v>81.30834486572085</v>
+        <v>74.50581502299471</v>
       </c>
       <c r="D6" t="n">
-        <v>38.48058301565798</v>
+        <v>43.63279496754524</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.02586959767568</v>
+        <v>22.93657161431823</v>
       </c>
       <c r="C7" t="n">
-        <v>65.33629146532947</v>
+        <v>47.72962813736718</v>
       </c>
       <c r="D7" t="n">
-        <v>36.47094546506476</v>
+        <v>36.77037851486003</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.678649705541805</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>41.80772598535042</v>
+        <v>27.45457454926205</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>34.46425315758427</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>27.84531013555227</v>
+        <v>24.84999788989526</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>33.62976760897449</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6608,7 +6608,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.510491133326828</v>
+        <v>7.497845766642635</v>
       </c>
       <c r="C21" t="n">
-        <v>86.37064803325852</v>
+        <v>85.28799559555996</v>
       </c>
       <c r="D21" t="n">
-        <v>7.510491133326828</v>
+        <v>7.497845766642635</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_77_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_77_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497630162837</v>
+        <v>10.84497630741194</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907183533087</v>
+        <v>37.78907185548361</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.14966761940202</v>
+        <v>4.656429361242622</v>
       </c>
       <c r="C2" t="n">
-        <v>5.821763886183585</v>
+        <v>11.00735526001524</v>
       </c>
       <c r="D2" t="n">
-        <v>23.40977400776519</v>
+        <v>27.0716929446058</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.00310947402876</v>
+        <v>13.23886779176824</v>
       </c>
       <c r="C3" t="n">
-        <v>31.80862561759665</v>
+        <v>22.8059991696534</v>
       </c>
       <c r="D3" t="n">
-        <v>68.98741117742337</v>
+        <v>43.60923302264332</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.90001026954963</v>
+        <v>29.26491731589317</v>
       </c>
       <c r="C4" t="n">
-        <v>75.68293052038661</v>
+        <v>59.60190312482386</v>
       </c>
       <c r="D4" t="n">
-        <v>97.11153766098174</v>
+        <v>47.23482729442679</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.30827844579606</v>
+        <v>37.60093707265284</v>
       </c>
       <c r="C5" t="n">
-        <v>104.8751985061655</v>
+        <v>120.6813365445392</v>
       </c>
       <c r="D5" t="n">
-        <v>77.11628216858696</v>
+        <v>39.63806355896497</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.12839763174064</v>
+        <v>35.74347041621788</v>
       </c>
       <c r="C6" t="n">
-        <v>110.4505437185832</v>
+        <v>178.7978553928376</v>
       </c>
       <c r="D6" t="n">
-        <v>52.08564270111029</v>
+        <v>36.74976181307086</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.17718191731671</v>
+        <v>24.97271635292611</v>
       </c>
       <c r="C7" t="n">
-        <v>78.63111887623978</v>
+        <v>170.0779722837174</v>
       </c>
       <c r="D7" t="n">
-        <v>41.08221443191203</v>
+        <v>37.36924461445059</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.60764507566654</v>
+        <v>12.93452600345173</v>
       </c>
       <c r="C8" t="n">
-        <v>45.47946239923349</v>
+        <v>110.485886635936</v>
       </c>
       <c r="D8" t="n">
-        <v>36.38356991938679</v>
+        <v>35.46563581591602</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.431249284071605</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>30.17499743772996</v>
+        <v>55.02499532762521</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>34.50155957034565</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>29.18245050873644</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.695513820388009</v>
+        <v>7.677555772604489</v>
       </c>
       <c r="C21" t="n">
-        <v>94.27004429975311</v>
+        <v>93.09036374282942</v>
       </c>
       <c r="D21" t="n">
-        <v>8.65745304793651</v>
+        <v>8.63725024418005</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.537278036130262</v>
+        <v>4.667228585989336</v>
       </c>
       <c r="C2" t="n">
-        <v>6.858489461868218</v>
+        <v>14.0036492533765</v>
       </c>
       <c r="D2" t="n">
-        <v>21.66226309420587</v>
+        <v>33.15263822471054</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.21418523044183</v>
+        <v>14.28933783531232</v>
       </c>
       <c r="C3" t="n">
-        <v>26.90970457340507</v>
+        <v>32.73637719810989</v>
       </c>
       <c r="D3" t="n">
-        <v>70.88709298514094</v>
+        <v>53.15182070792231</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.66653424238812</v>
+        <v>26.98039040811084</v>
       </c>
       <c r="C4" t="n">
-        <v>76.74223629326892</v>
+        <v>57.63644422092175</v>
       </c>
       <c r="D4" t="n">
-        <v>106.6452896169225</v>
+        <v>56.58990116819465</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.93507544946203</v>
+        <v>40.34983064454391</v>
       </c>
       <c r="C5" t="n">
-        <v>121.810346404423</v>
+        <v>115.3553552490002</v>
       </c>
       <c r="D5" t="n">
-        <v>92.65243958829274</v>
+        <v>45.89670517353839</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.54728510628455</v>
+        <v>42.98876847355934</v>
       </c>
       <c r="C6" t="n">
-        <v>136.050596854523</v>
+        <v>183.7488090653543</v>
       </c>
       <c r="D6" t="n">
-        <v>62.26931163726245</v>
+        <v>40.57366912111219</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43.35790561035613</v>
+        <v>32.93763547748049</v>
       </c>
       <c r="C7" t="n">
-        <v>117.1980956898715</v>
+        <v>212.2980323048515</v>
       </c>
       <c r="D7" t="n">
-        <v>46.35223610830891</v>
+        <v>39.16584291322225</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.36974333606933</v>
+        <v>19.27661617288612</v>
       </c>
       <c r="C8" t="n">
-        <v>72.60024272905163</v>
+        <v>162.6412334240478</v>
       </c>
       <c r="D8" t="n">
-        <v>38.7201294554942</v>
+        <v>37.46840113257952</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.64687392610741</v>
+        <v>9.873436661610169</v>
       </c>
       <c r="C9" t="n">
-        <v>42.82187136383736</v>
+        <v>92.74374212478766</v>
       </c>
       <c r="D9" t="n">
-        <v>35.94374694788421</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.8329640215578</v>
+        <v>5.978843518863076</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>47.11898106532567</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>30.8092064546734</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
         <v>31.34327720578367</v>
@@ -1276,7 +1276,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.878114933077453</v>
+        <v>7.855354287319452</v>
       </c>
       <c r="C21" t="n">
-        <v>103.4002584966416</v>
+        <v>101.1376864492379</v>
       </c>
       <c r="D21" t="n">
-        <v>9.847643666346816</v>
+        <v>9.819192859149315</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.584802836561609</v>
+        <v>6.10647072041516</v>
       </c>
       <c r="C2" t="n">
-        <v>7.384706231344508</v>
+        <v>16.56993775227766</v>
       </c>
       <c r="D2" t="n">
-        <v>24.63990388118645</v>
+        <v>25.94857357094745</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.65030219530566</v>
+        <v>14.5740446695439</v>
       </c>
       <c r="C3" t="n">
-        <v>26.56609287691869</v>
+        <v>42.49004063980195</v>
       </c>
       <c r="D3" t="n">
-        <v>71.0245376637355</v>
+        <v>63.25891332314323</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.30092318578082</v>
+        <v>26.41883072128167</v>
       </c>
       <c r="C4" t="n">
-        <v>71.40741926839175</v>
+        <v>68.30607827067608</v>
       </c>
       <c r="D4" t="n">
-        <v>115.3239393224643</v>
+        <v>66.07260224351459</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.11317269455821</v>
+        <v>40.12893741108838</v>
       </c>
       <c r="C5" t="n">
-        <v>130.4006388165826</v>
+        <v>109.980286568249</v>
       </c>
       <c r="D5" t="n">
-        <v>105.1206354322272</v>
+        <v>53.55433726666352</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>63.83912621635311</v>
+        <v>47.57745724320893</v>
       </c>
       <c r="C6" t="n">
-        <v>159.7588221643792</v>
+        <v>182.5010077332566</v>
       </c>
       <c r="D6" t="n">
-        <v>74.34480839949822</v>
+        <v>44.27682146153116</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>53.11942303368217</v>
+        <v>40.48334833232147</v>
       </c>
       <c r="C7" t="n">
-        <v>151.0340303167378</v>
+        <v>236.7317691681461</v>
       </c>
       <c r="D7" t="n">
-        <v>51.74203100462389</v>
+        <v>41.62119392154352</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>35.549084370777</v>
+        <v>26.20284622634736</v>
       </c>
       <c r="C8" t="n">
-        <v>108.9838126484384</v>
+        <v>211.8758807920254</v>
       </c>
       <c r="D8" t="n">
-        <v>41.80772598535042</v>
+        <v>38.88702656521616</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18.41562343626167</v>
+        <v>13.64531134132641</v>
       </c>
       <c r="C9" t="n">
-        <v>62.90155715879737</v>
+        <v>137.6734258096429</v>
       </c>
       <c r="D9" t="n">
-        <v>37.16405934426299</v>
+        <v>36.94218436310322</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>40.85543071223102</v>
+        <v>73.027302980399</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.508586368528851</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>34.82848155585983</v>
+        <v>41.75863860013807</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>33.1958351236974</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.95941385342317</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1570,7 +1570,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
         <v>27.3485457972034</v>
@@ -1587,7 +1587,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -1601,7 +1601,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.045332030541344</v>
+        <v>8.016687329057383</v>
       </c>
       <c r="C21" t="n">
-        <v>111.6289819237612</v>
+        <v>109.2273648584068</v>
       </c>
       <c r="D21" t="n">
-        <v>11.06233154199435</v>
+        <v>11.0229450774539</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.685521939471531</v>
+        <v>5.536075304247763</v>
       </c>
       <c r="C2" t="n">
-        <v>5.020657759518188</v>
+        <v>11.40005434171396</v>
       </c>
       <c r="D2" t="n">
-        <v>20.25738212942869</v>
+        <v>21.36577528752333</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.66074156715388</v>
+        <v>17.84326452468578</v>
       </c>
       <c r="C3" t="n">
-        <v>41.00760160638927</v>
+        <v>60.91253630999335</v>
       </c>
       <c r="D3" t="n">
-        <v>78.65271732573322</v>
+        <v>65.49729808882596</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.43984833369835</v>
+        <v>19.27170743436488</v>
       </c>
       <c r="C4" t="n">
-        <v>104.8457460750381</v>
+        <v>92.2744667221577</v>
       </c>
       <c r="D4" t="n">
-        <v>114.1625317883403</v>
+        <v>62.37141339850411</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.95650966803944</v>
+        <v>26.80171232593793</v>
       </c>
       <c r="C5" t="n">
-        <v>95.45042054539616</v>
+        <v>109.0476262492145</v>
       </c>
       <c r="D5" t="n">
-        <v>72.67387380687015</v>
+        <v>40.84070449666732</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.96610616090365</v>
+        <v>25.1170332654504</v>
       </c>
       <c r="C6" t="n">
-        <v>99.46184166494862</v>
+        <v>155.8946632004638</v>
       </c>
       <c r="D6" t="n">
-        <v>34.05290086950487</v>
+        <v>27.4113776502752</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.53543771390878</v>
+        <v>17.36711688812607</v>
       </c>
       <c r="C7" t="n">
-        <v>76.59497413763189</v>
+        <v>148.9978855781299</v>
       </c>
       <c r="D7" t="n">
-        <v>29.34443887993716</v>
+        <v>27.30829414132927</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.76762889372977</v>
+        <v>9.429686699290613</v>
       </c>
       <c r="C8" t="n">
-        <v>46.31394794784328</v>
+        <v>101.4734427109503</v>
       </c>
       <c r="D8" t="n">
-        <v>27.37112599440107</v>
+        <v>27.20422888467911</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.434374453633594</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>31.17343485294896</v>
+        <v>55.69062027110455</v>
       </c>
       <c r="D9" t="n">
-        <v>27.73437264497238</v>
+        <v>27.40156017323271</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.98589567924205</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
         <v>28.61303684027329</v>
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.43141351498762</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>26.4698816019025</v>
       </c>
     </row>
     <row r="13">
@@ -1867,7 +1867,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
         <v>22.63419332141022</v>
@@ -1884,7 +1884,7 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
         <v>23.66110142005238</v>
@@ -1898,7 +1898,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>22.57528845915541</v>
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
         <v>7.397468951499714</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.228788272818512</v>
+        <v>3.387029579651496</v>
       </c>
       <c r="C2" t="n">
-        <v>2.852958828541231</v>
+        <v>4.902848035008571</v>
       </c>
       <c r="D2" t="n">
-        <v>14.59171612822034</v>
+        <v>15.00306841629976</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.56042337487146</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="C3" t="n">
-        <v>30.5176273865121</v>
+        <v>53.66232951413066</v>
       </c>
       <c r="D3" t="n">
-        <v>77.19973072344794</v>
+        <v>67.97130230352791</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.73485567105791</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="C4" t="n">
-        <v>106.5176624153704</v>
+        <v>124.3471824721968</v>
       </c>
       <c r="D4" t="n">
-        <v>126.746573861376</v>
+        <v>76.61460909171683</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.25165587411923</v>
+        <v>29.10881943091793</v>
       </c>
       <c r="C5" t="n">
-        <v>142.8933783531233</v>
+        <v>139.5799798512903</v>
       </c>
       <c r="D5" t="n">
-        <v>90.17352663506955</v>
+        <v>50.24093876483053</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.68813269188156</v>
+        <v>29.74597369097411</v>
       </c>
       <c r="C6" t="n">
-        <v>125.7461729507485</v>
+        <v>171.5928089913703</v>
       </c>
       <c r="D6" t="n">
-        <v>42.78751019418875</v>
+        <v>31.67805317293184</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.09815907489146</v>
+        <v>16.22927129890402</v>
       </c>
       <c r="C7" t="n">
-        <v>102.1066699801895</v>
+        <v>183.9716657942183</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>29.88341836956866</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.59796646734432</v>
+        <v>8.011061266653972</v>
       </c>
       <c r="C8" t="n">
-        <v>64.00504157837081</v>
+        <v>132.2659594546515</v>
       </c>
       <c r="D8" t="n">
-        <v>28.53940576245478</v>
+        <v>27.95526587842792</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>4.326562132615692</v>
       </c>
       <c r="C9" t="n">
-        <v>36.38749691020377</v>
+        <v>61.34843229067891</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -2136,10 +2136,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>34.44952694202058</v>
       </c>
       <c r="D10" t="n">
         <v>29.89421759431538</v>
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.14219885286231</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2181,7 +2181,7 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
         <v>25.23582473766426</v>
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
         <v>6.018113427032947</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.974916528046087</v>
+        <v>3.374266859496287</v>
       </c>
       <c r="C2" t="n">
-        <v>7.856926877087224</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="D2" t="n">
-        <v>16.467835991036</v>
+        <v>16.17822041828319</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.59630607157209</v>
+        <v>15.18272824617692</v>
       </c>
       <c r="C3" t="n">
-        <v>20.10619298297468</v>
+        <v>35.75525138866883</v>
       </c>
       <c r="D3" t="n">
-        <v>71.27488332831844</v>
+        <v>64.35847075189966</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.29864089520283</v>
+        <v>30.83473189498382</v>
       </c>
       <c r="C4" t="n">
-        <v>90.73017758337748</v>
+        <v>129.0438634893135</v>
       </c>
       <c r="D4" t="n">
-        <v>135.6677152498667</v>
+        <v>90.61531310198059</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.81740459367266</v>
+        <v>33.60031517784709</v>
       </c>
       <c r="C5" t="n">
-        <v>171.0204500797944</v>
+        <v>182.5314419120882</v>
       </c>
       <c r="D5" t="n">
-        <v>112.4837432140783</v>
+        <v>63.61725123519332</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.13468902859362</v>
+        <v>34.09315252537899</v>
       </c>
       <c r="C6" t="n">
-        <v>173.4846368174539</v>
+        <v>196.9111005361913</v>
       </c>
       <c r="D6" t="n">
-        <v>58.32464936159877</v>
+        <v>38.56108632740622</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.45854259780804</v>
+        <v>23.83487076370406</v>
       </c>
       <c r="C7" t="n">
-        <v>140.4939869639441</v>
+        <v>213.914970773746</v>
       </c>
       <c r="D7" t="n">
-        <v>36.77037851486003</v>
+        <v>31.91956310817654</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.52143120414207</v>
+        <v>11.43245201595411</v>
       </c>
       <c r="C8" t="n">
-        <v>96.80032363873549</v>
+        <v>183.3364750295706</v>
       </c>
       <c r="D8" t="n">
-        <v>30.29182541453534</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.878124415953151</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>55.24687030878498</v>
+        <v>105.0578035791554</v>
       </c>
       <c r="D9" t="n">
         <v>29.39843500367073</v>
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.847068342315751</v>
+        <v>2.562361508084175</v>
       </c>
       <c r="C10" t="n">
-        <v>36.86953503298896</v>
+        <v>49.39663573917827</v>
       </c>
       <c r="D10" t="n">
-        <v>30.60598467989432</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>34.29539255245382</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2523,7 +2523,7 @@
         <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
         <v>4.212679398923063</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.514656781203581</v>
+        <v>2.009637550593221</v>
       </c>
       <c r="C2" t="n">
-        <v>3.606941065402781</v>
+        <v>4.948990177108171</v>
       </c>
       <c r="D2" t="n">
-        <v>11.36274792895258</v>
+        <v>11.28813510342983</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.45533531278805</v>
+        <v>15.03055735201867</v>
       </c>
       <c r="C3" t="n">
-        <v>26.05558407071035</v>
+        <v>40.09457624143974</v>
       </c>
       <c r="D3" t="n">
-        <v>70.79873569175872</v>
+        <v>64.63336010908876</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>52.30162719604458</v>
+        <v>34.02541193378595</v>
       </c>
       <c r="C4" t="n">
-        <v>84.62959734918779</v>
+        <v>127.3081335482051</v>
       </c>
       <c r="D4" t="n">
-        <v>143.3763982236127</v>
+        <v>99.15357288581511</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.6827252317416</v>
+        <v>35.46563581591603</v>
       </c>
       <c r="C5" t="n">
-        <v>198.0185119465817</v>
+        <v>226.464651677133</v>
       </c>
       <c r="D5" t="n">
-        <v>120.7549676223577</v>
+        <v>68.01057221169781</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.72838434775569</v>
+        <v>28.33716573537994</v>
       </c>
       <c r="C6" t="n">
-        <v>207.2557760958399</v>
+        <v>237.4445180014294</v>
       </c>
       <c r="D6" t="n">
-        <v>56.67433147075987</v>
+        <v>38.88309957439917</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.24061030299848</v>
+        <v>7.545712854840985</v>
       </c>
       <c r="C7" t="n">
-        <v>139.8951208643535</v>
+        <v>230.6832215622815</v>
       </c>
       <c r="D7" t="n">
-        <v>36.53083207502382</v>
+        <v>32.5184292077671</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>3.838633523605028</v>
       </c>
       <c r="C8" t="n">
-        <v>71.01472018669303</v>
+        <v>131.2645767963198</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>28.06718511671205</v>
+        <v>37.71874679716245</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.90832191507333</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.20360698987336</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>19.72429312602266</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2820,7 +2820,7 @@
         <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
         <v>3.21031499288707</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.085052197370977</v>
+        <v>2.52996383384403</v>
       </c>
       <c r="C2" t="n">
-        <v>4.030074325933156</v>
+        <v>11.98321247803657</v>
       </c>
       <c r="D2" t="n">
-        <v>13.32427984203771</v>
+        <v>9.315803965597985</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.40286071610646</v>
+        <v>11.15265392024377</v>
       </c>
       <c r="C3" t="n">
-        <v>19.86075605691298</v>
+        <v>29.71259426902972</v>
       </c>
       <c r="D3" t="n">
-        <v>64.13757751844412</v>
+        <v>59.79334392715199</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.18301565027996</v>
+        <v>31.48563062289946</v>
       </c>
       <c r="C4" t="n">
-        <v>75.56806603898974</v>
+        <v>114.0221418666331</v>
       </c>
       <c r="D4" t="n">
-        <v>145.6481624112398</v>
+        <v>106.7091032176986</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.68459091615885</v>
+        <v>42.11697651218817</v>
       </c>
       <c r="C5" t="n">
-        <v>179.8807231106219</v>
+        <v>232.0115262061275</v>
       </c>
       <c r="D5" t="n">
-        <v>142.0343491119073</v>
+        <v>83.59581701661591</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.99884799250906</v>
+        <v>36.02523200733671</v>
       </c>
       <c r="C6" t="n">
-        <v>257.0068227562513</v>
+        <v>292.9112997959657</v>
       </c>
       <c r="D6" t="n">
-        <v>74.90833158173589</v>
+        <v>48.1409804254466</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.63713856452295</v>
+        <v>15.63040519931347</v>
       </c>
       <c r="C7" t="n">
-        <v>208.8844955371853</v>
+        <v>283.1438918864141</v>
       </c>
       <c r="D7" t="n">
-        <v>42.57937968088841</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.592435834017332</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C8" t="n">
-        <v>119.1645363414778</v>
+        <v>200.8606715503762</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71321616383547</v>
+        <v>32.71183350550372</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>50.25468323268996</v>
+        <v>81.6499930667987</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>29.32480392585223</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.48478774391545</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
         <v>21.47965802121596</v>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
         <v>4.722206457427158</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.96095107600838</v>
+        <v>1.644427404613408</v>
       </c>
       <c r="C2" t="n">
-        <v>2.654645792283375</v>
+        <v>6.856525966459724</v>
       </c>
       <c r="D2" t="n">
-        <v>9.824349276397832</v>
+        <v>8.179921871784424</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.69952844923824</v>
+        <v>10.18563243156066</v>
       </c>
       <c r="C3" t="n">
-        <v>18.11815388187489</v>
+        <v>37.43894870145211</v>
       </c>
       <c r="D3" t="n">
-        <v>60.94198874112075</v>
+        <v>55.15458602458581</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.55014823393926</v>
+        <v>28.34600146471816</v>
       </c>
       <c r="C4" t="n">
-        <v>66.28956848615313</v>
+        <v>100.4553703416464</v>
       </c>
       <c r="D4" t="n">
-        <v>145.4439588887565</v>
+        <v>110.5634447045715</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>69.28684422721865</v>
+        <v>45.0622196249286</v>
       </c>
       <c r="C5" t="n">
-        <v>170.4314014572463</v>
+        <v>229.4589821750858</v>
       </c>
       <c r="D5" t="n">
-        <v>156.3433219013046</v>
+        <v>95.49950793060849</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.97496725243766</v>
+        <v>41.78121879733577</v>
       </c>
       <c r="C6" t="n">
-        <v>279.5074983898839</v>
+        <v>331.3918828116236</v>
       </c>
       <c r="D6" t="n">
-        <v>89.11716610529999</v>
+        <v>55.34602682691394</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.25974653546468</v>
+        <v>14.07335334037803</v>
       </c>
       <c r="C7" t="n">
-        <v>263.560970429803</v>
+        <v>338.2994596587041</v>
       </c>
       <c r="D7" t="n">
-        <v>48.32849423695774</v>
+        <v>38.80652325346792</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>160.8888137719673</v>
+        <v>250.5125616926586</v>
       </c>
       <c r="D8" t="n">
-        <v>35.13184159647211</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>59.68436993198057</v>
+        <v>91.52342972840887</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>31.8390597964283</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
         <v>16.3902779224005</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
         <v>3.719842051391165</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.630903920932204</v>
+        <v>2.443570035870311</v>
       </c>
       <c r="C2" t="n">
-        <v>6.053456344385832</v>
+        <v>20.469439633546</v>
       </c>
       <c r="D2" t="n">
-        <v>14.99914142548277</v>
+        <v>13.13774777823082</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.48430471782994</v>
+        <v>8.025787482217675</v>
       </c>
       <c r="C3" t="n">
-        <v>14.3433339590459</v>
+        <v>32.63820242768521</v>
       </c>
       <c r="D3" t="n">
-        <v>55.62091618410305</v>
+        <v>50.44219704420112</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.92629647338603</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="C4" t="n">
-        <v>56.61542660850506</v>
+        <v>96.14157092918589</v>
       </c>
       <c r="D4" t="n">
-        <v>142.8914148577148</v>
+        <v>110.5506819844163</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>68.89414514551993</v>
+        <v>44.00684084286328</v>
       </c>
       <c r="C5" t="n">
-        <v>149.1520199676967</v>
+        <v>210.3885330200915</v>
       </c>
       <c r="D5" t="n">
-        <v>166.6516727958961</v>
+        <v>108.3358591636355</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>72.93600044390405</v>
+        <v>48.66425195181016</v>
       </c>
       <c r="C6" t="n">
-        <v>277.0923990374368</v>
+        <v>345.4799623675653</v>
       </c>
       <c r="D6" t="n">
-        <v>110.4102920627091</v>
+        <v>67.26051696565324</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.38731698375453</v>
+        <v>25.33203601268044</v>
       </c>
       <c r="C7" t="n">
-        <v>324.2261063183261</v>
+        <v>397.587203518169</v>
       </c>
       <c r="D7" t="n">
-        <v>58.56910453995621</v>
+        <v>43.47767883027424</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>7.34347282776614</v>
       </c>
       <c r="C8" t="n">
-        <v>233.5725050558799</v>
+        <v>323.94728997032</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>35.71598148049896</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.773437264497239</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>111.6031155233689</v>
+        <v>168.0702982285327</v>
       </c>
       <c r="D9" t="n">
-        <v>34.50155957034565</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -3691,10 +3691,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>45.12603322570465</v>
+        <v>57.51078051477815</v>
       </c>
       <c r="D10" t="n">
         <v>26.47773558353648</v>
@@ -3711,7 +3711,7 @@
         <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>19.30999559483051</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
         <v>16.65044106402591</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.849653732529996</v>
+        <v>4.547455366071226</v>
       </c>
       <c r="C2" t="n">
-        <v>2.956042337487146</v>
+        <v>12.12949288596934</v>
       </c>
       <c r="D2" t="n">
-        <v>19.18531363639117</v>
+        <v>5.273948667213865</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.315361997241479</v>
+        <v>1.783835578616454</v>
       </c>
       <c r="C2" t="n">
-        <v>3.43808046027233</v>
+        <v>12.11869366122263</v>
       </c>
       <c r="D2" t="n">
-        <v>11.03877118655113</v>
+        <v>9.774280143481244</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.24578108342697</v>
+        <v>10.79431600819368</v>
       </c>
       <c r="C3" t="n">
-        <v>19.27661617288612</v>
+        <v>50.46674073680729</v>
       </c>
       <c r="D3" t="n">
-        <v>61.8844665371977</v>
+        <v>55.36566178099887</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>52.99081408442584</v>
+        <v>33.43832680664636</v>
       </c>
       <c r="C4" t="n">
-        <v>82.1025787584565</v>
+        <v>134.64669763745</v>
       </c>
       <c r="D4" t="n">
-        <v>147.5370449942107</v>
+        <v>111.1505298317111</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.0005494460103</v>
+        <v>27.80800372279091</v>
       </c>
       <c r="C5" t="n">
-        <v>228.1581664669588</v>
+        <v>300.562059655161</v>
       </c>
       <c r="D5" t="n">
-        <v>154.5761760336603</v>
+        <v>98.49383842856128</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>23.82898027747859</v>
+        <v>15.6981457909065</v>
       </c>
       <c r="C6" t="n">
-        <v>270.5716307858295</v>
+        <v>322.8182801104363</v>
       </c>
       <c r="D6" t="n">
-        <v>87.62785483795757</v>
+        <v>57.47936458824226</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.246279805045708</v>
+        <v>4.850815406683489</v>
       </c>
       <c r="C7" t="n">
-        <v>164.2689711176891</v>
+        <v>227.8086642842468</v>
       </c>
       <c r="D7" t="n">
-        <v>34.55457394637499</v>
+        <v>30.18285141936394</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.919316761802514</v>
+        <v>1.50207398749762</v>
       </c>
       <c r="C8" t="n">
-        <v>82.19682653806419</v>
+        <v>123.8376554136927</v>
       </c>
       <c r="D8" t="n">
-        <v>25.36836067773758</v>
+        <v>24.11663235482289</v>
       </c>
     </row>
     <row r="9">
@@ -4299,10 +4299,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>43.82030877905637</v>
       </c>
       <c r="D9" t="n">
         <v>20.1906232855399</v>
@@ -4319,7 +4319,7 @@
         <v>22.06477965294707</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>18.93300447639974</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.52575910558656</v>
+        <v>15.45958109877452</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
         <v>13.4519070435898</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.525096153051801</v>
+        <v>5.932701376763475</v>
       </c>
       <c r="C2" t="n">
-        <v>3.512693285795088</v>
+        <v>8.604036880019047</v>
       </c>
       <c r="D2" t="n">
-        <v>16.60822591274329</v>
+        <v>6.361725123519331</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.5445922384165</v>
+        <v>9.665306148309849</v>
       </c>
       <c r="C3" t="n">
-        <v>7.446556336712057</v>
+        <v>30.56180603320321</v>
       </c>
       <c r="D3" t="n">
-        <v>19.25207248027995</v>
+        <v>7.564366061221674</v>
       </c>
     </row>
     <row r="4">
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39702620451533</v>
+        <v>13.39823357613089</v>
       </c>
       <c r="C21" t="n">
-        <v>70.1373724824626</v>
+        <v>70.14369342797936</v>
       </c>
       <c r="D21" t="n">
-        <v>1.57612072994298</v>
+        <v>1.576262773662457</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.043237956715865</v>
+        <v>3.826852551154067</v>
       </c>
       <c r="C2" t="n">
-        <v>7.042076282562371</v>
+        <v>10.004009106275</v>
       </c>
       <c r="D2" t="n">
-        <v>21.69269727303752</v>
+        <v>7.677267047210058</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.4217349066654</v>
+        <v>16.13502351929633</v>
       </c>
       <c r="C3" t="n">
-        <v>11.3588209381356</v>
+        <v>32.43203540979338</v>
       </c>
       <c r="D3" t="n">
-        <v>28.54922323949725</v>
+        <v>11.07902284242526</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16.85955332503048</v>
+        <v>11.34605821798039</v>
       </c>
       <c r="C4" t="n">
-        <v>11.90761790480956</v>
+        <v>47.0944373727195</v>
       </c>
       <c r="D4" t="n">
-        <v>25.15532142591602</v>
+        <v>19.02921575141593</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.092505268377454</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.448699758569798</v>
+        <v>5.424156065963628</v>
       </c>
       <c r="D5" t="n">
         <v>29.10881943091793</v>
@@ -4885,7 +4885,7 @@
         <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>35.01894061048373</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44004136359705</v>
+        <v>15.44140598968469</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13917813375195</v>
+        <v>86.14679131087247</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250535023915168</v>
+        <v>3.250822313617829</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.122759520759856</v>
+        <v>5.301437602932777</v>
       </c>
       <c r="C2" t="n">
-        <v>6.10352547730242</v>
+        <v>10.12672756930585</v>
       </c>
       <c r="D2" t="n">
-        <v>24.8234907018806</v>
+        <v>12.76664714602552</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.18825887950391</v>
+        <v>14.51023106876786</v>
       </c>
       <c r="C3" t="n">
-        <v>21.08794068722149</v>
+        <v>36.37375244234433</v>
       </c>
       <c r="D3" t="n">
-        <v>39.27972564691488</v>
+        <v>14.64767574736241</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.71986741358695</v>
+        <v>22.62830283518473</v>
       </c>
       <c r="C4" t="n">
-        <v>21.63281066307847</v>
+        <v>67.19572161717294</v>
       </c>
       <c r="D4" t="n">
-        <v>33.80844569114741</v>
+        <v>20.31825048709199</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>14.79984664152067</v>
+        <v>10.25926350937917</v>
       </c>
       <c r="C5" t="n">
-        <v>14.87347771933918</v>
+        <v>51.88536616944394</v>
       </c>
       <c r="D5" t="n">
-        <v>31.44047022850411</v>
+        <v>29.30516897176729</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.15600007398401</v>
+        <v>12.11574841810989</v>
       </c>
       <c r="D6" t="n">
-        <v>36.8302651248191</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.24947139453248</v>
+        <v>37.78845088416398</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.79113408536946</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5280,7 +5280,7 @@
         <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5294,7 +5294,7 @@
         <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>45.00822350119503</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5319,7 +5319,7 @@
         <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73473489825746</v>
+        <v>16.73422966254635</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0818828793705</v>
+        <v>102.0788009415327</v>
       </c>
       <c r="D21" t="n">
-        <v>5.020420469477239</v>
+        <v>5.020268898763906</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.633268326968198</v>
+        <v>4.417864669110647</v>
       </c>
       <c r="C2" t="n">
-        <v>9.280461048245099</v>
+        <v>6.222316949516284</v>
       </c>
       <c r="D2" t="n">
-        <v>25.31141931089127</v>
+        <v>10.80904222375738</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.29486846863931</v>
+        <v>16.42954783057037</v>
       </c>
       <c r="C3" t="n">
-        <v>22.57528845915541</v>
+        <v>38.04763227808514</v>
       </c>
       <c r="D3" t="n">
-        <v>49.40645321622073</v>
+        <v>21.08794068722149</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.37000537797658</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="C4" t="n">
-        <v>38.81143199198916</v>
+        <v>80.50723873905544</v>
       </c>
       <c r="D4" t="n">
-        <v>44.91201222617884</v>
+        <v>22.93460811890974</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.2869166760141</v>
+        <v>22.06477965294707</v>
       </c>
       <c r="C5" t="n">
-        <v>28.66703296400687</v>
+        <v>90.88529372064848</v>
       </c>
       <c r="D5" t="n">
-        <v>36.59464567579986</v>
+        <v>29.82058651649687</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.96103319146639</v>
+        <v>9.861655689159212</v>
       </c>
       <c r="C6" t="n">
-        <v>18.23400011097601</v>
+        <v>48.26173539306896</v>
       </c>
       <c r="D6" t="n">
-        <v>38.84284791852506</v>
+        <v>38.07806645691679</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.40538935305847</v>
+        <v>39.76470901281281</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.79389940203295</v>
+        <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
-        <v>40.22220344299182</v>
+        <v>40.05530633326986</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>41.82343394861835</v>
+        <v>42.26718391093791</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>10.10709261522091</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5571,7 +5571,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
         <v>33.58460721457913</v>
@@ -5588,10 +5588,10 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
         <v>43.71722527011046</v>
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>41.33157834879071</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06325375715697</v>
+        <v>18.05625894831553</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8412268919288</v>
+        <v>117.7955940913918</v>
       </c>
       <c r="D21" t="n">
-        <v>6.881239526535988</v>
+        <v>6.878574837453537</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.8795070742849</v>
+        <v>4.684900044665779</v>
       </c>
       <c r="C2" t="n">
-        <v>6.865361695797945</v>
+        <v>5.115887286830128</v>
       </c>
       <c r="D2" t="n">
-        <v>23.52365674145782</v>
+        <v>17.19727453529138</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.00387023755476</v>
+        <v>13.96536109291088</v>
       </c>
       <c r="C3" t="n">
-        <v>28.46577468463627</v>
+        <v>28.34305622160542</v>
       </c>
       <c r="D3" t="n">
-        <v>54.24156065963628</v>
+        <v>23.15451960466102</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.2701859073129</v>
+        <v>21.10953913671491</v>
       </c>
       <c r="C4" t="n">
-        <v>40.47058561216627</v>
+        <v>73.41116633275949</v>
       </c>
       <c r="D4" t="n">
-        <v>50.91049069912684</v>
+        <v>24.45337181737955</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.15728492132452</v>
+        <v>18.33413837680919</v>
       </c>
       <c r="C5" t="n">
-        <v>38.77903431774902</v>
+        <v>90.56622571676827</v>
       </c>
       <c r="D5" t="n">
-        <v>36.12831551628263</v>
+        <v>25.18182861393069</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.93336432929824</v>
+        <v>10.78744377426395</v>
       </c>
       <c r="C6" t="n">
-        <v>21.93715245139498</v>
+        <v>65.69070238656259</v>
       </c>
       <c r="D6" t="n">
-        <v>32.28182801104362</v>
+        <v>30.3497485290859</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.048547605864599</v>
+        <v>5.150248456478767</v>
       </c>
       <c r="C7" t="n">
-        <v>15.39085875947725</v>
+        <v>29.2845522699781</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>30.84160412891355</v>
       </c>
     </row>
     <row r="8">
@@ -5843,7 +5843,7 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
         <v>30.20837685967435</v>
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>30.06405994715006</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
         <v>30.43908757017236</v>
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.061382619537042</v>
+        <v>7.054933681079971</v>
       </c>
       <c r="C21" t="n">
-        <v>66.20046205815977</v>
+        <v>66.14000326012473</v>
       </c>
       <c r="D21" t="n">
-        <v>5.296036964652782</v>
+        <v>5.291200260809978</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.33718143091316</v>
+        <v>4.628940425523711</v>
       </c>
       <c r="C2" t="n">
-        <v>9.789988106749192</v>
+        <v>5.703954161673968</v>
       </c>
       <c r="D2" t="n">
-        <v>24.64775786282042</v>
+        <v>13.46565151144925</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.51285751671111</v>
+        <v>15.63924092865169</v>
       </c>
       <c r="C3" t="n">
-        <v>27.41039590257095</v>
+        <v>22.95817006381166</v>
       </c>
       <c r="D3" t="n">
-        <v>61.31505286873454</v>
+        <v>32.00497515844602</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.28593492830985</v>
+        <v>24.88730430265664</v>
       </c>
       <c r="C4" t="n">
-        <v>60.22727641242908</v>
+        <v>72.04555527615219</v>
       </c>
       <c r="D4" t="n">
-        <v>68.39541731176254</v>
+        <v>30.68157925312132</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.13398501832986</v>
+        <v>26.26175108860219</v>
       </c>
       <c r="C5" t="n">
-        <v>61.21196935978864</v>
+        <v>118.3005983617407</v>
       </c>
       <c r="D5" t="n">
-        <v>47.46750150033328</v>
+        <v>28.81429511964389</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.20382797405162</v>
+        <v>18.75727163733956</v>
       </c>
       <c r="C6" t="n">
-        <v>45.64537776125121</v>
+        <v>111.7788483624291</v>
       </c>
       <c r="D6" t="n">
-        <v>36.66925850132262</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.81573453123786</v>
+        <v>9.641744203407924</v>
       </c>
       <c r="C7" t="n">
-        <v>25.15237618280328</v>
+        <v>67.19277637406019</v>
       </c>
       <c r="D7" t="n">
-        <v>33.83593462686632</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>20.11110172149591</v>
+        <v>30.70906818884022</v>
       </c>
       <c r="D8" t="n">
         <v>32.21114217633784</v>
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>32.76190263842031</v>
       </c>
     </row>
     <row r="13">
@@ -6224,7 +6224,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
         <v>31.21957699504857</v>
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6266,7 +6266,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
         <v>26.45221014322606</v>
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.285987180917035</v>
+        <v>7.275852294132944</v>
       </c>
       <c r="C21" t="n">
-        <v>75.59211700201425</v>
+        <v>75.48696755162931</v>
       </c>
       <c r="D21" t="n">
-        <v>6.375238783302406</v>
+        <v>6.366370757366326</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.148284961070273</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C2" t="n">
-        <v>7.804894248762142</v>
+        <v>5.960190312482386</v>
       </c>
       <c r="D2" t="n">
-        <v>22.41919057418016</v>
+        <v>21.92733497435251</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.88944772451438</v>
+        <v>15.86504290062846</v>
       </c>
       <c r="C3" t="n">
-        <v>33.88993075059989</v>
+        <v>22.49674864281566</v>
       </c>
       <c r="D3" t="n">
-        <v>66.80793127399544</v>
+        <v>35.34782609140641</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.93905919354124</v>
+        <v>28.20561154301086</v>
       </c>
       <c r="C4" t="n">
-        <v>64.64317758613123</v>
+        <v>63.5455836527833</v>
       </c>
       <c r="D4" t="n">
-        <v>83.12359637087319</v>
+        <v>39.83244960440584</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.34983064454391</v>
+        <v>32.25041208450773</v>
       </c>
       <c r="C5" t="n">
-        <v>90.34533248331273</v>
+        <v>126.9154344665064</v>
       </c>
       <c r="D5" t="n">
-        <v>62.14462967882311</v>
+        <v>33.15852871093603</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.38749691020379</v>
+        <v>27.97490083251287</v>
       </c>
       <c r="C6" t="n">
-        <v>74.50581502299471</v>
+        <v>153.9223320626319</v>
       </c>
       <c r="D6" t="n">
-        <v>43.63279496754524</v>
+        <v>34.29441080474959</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.93657161431823</v>
+        <v>16.40893112878119</v>
       </c>
       <c r="C7" t="n">
-        <v>47.72962813736718</v>
+        <v>117.9766216193392</v>
       </c>
       <c r="D7" t="n">
-        <v>36.77037851486003</v>
+        <v>35.09355343600648</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>8.261406931236909</v>
       </c>
       <c r="C8" t="n">
-        <v>27.45457454926205</v>
+        <v>62.75331325545612</v>
       </c>
       <c r="D8" t="n">
-        <v>34.46425315758427</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>24.84999788989526</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -6496,7 +6496,7 @@
         <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>33.84673385161303</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
         <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6577,7 +6577,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.497845766642635</v>
+        <v>7.484031990776549</v>
       </c>
       <c r="C21" t="n">
-        <v>85.28799559555996</v>
+        <v>84.19535989623618</v>
       </c>
       <c r="D21" t="n">
-        <v>7.497845766642635</v>
+        <v>7.484031990776549</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_77_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_77_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497630741194</v>
+        <v>10.84497632314462</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907185548361</v>
+        <v>37.78907191030378</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.656429361242622</v>
+        <v>1.32045066221196</v>
       </c>
       <c r="C2" t="n">
-        <v>11.00735526001524</v>
+        <v>3.660937189136356</v>
       </c>
       <c r="D2" t="n">
-        <v>27.0716929446058</v>
+        <v>13.22021458538755</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.23886779176824</v>
+        <v>10.97593933347934</v>
       </c>
       <c r="C3" t="n">
-        <v>22.8059991696534</v>
+        <v>48.2479909252095</v>
       </c>
       <c r="D3" t="n">
-        <v>43.60923302264332</v>
+        <v>66.9601021681537</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.26491731589317</v>
+        <v>18.08477445993049</v>
       </c>
       <c r="C4" t="n">
-        <v>59.60190312482386</v>
+        <v>172.6157900991954</v>
       </c>
       <c r="D4" t="n">
-        <v>47.23482729442679</v>
+        <v>82.66413844528567</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.60093707265284</v>
+        <v>15.87976911619216</v>
       </c>
       <c r="C5" t="n">
-        <v>120.6813365445392</v>
+        <v>211.5420865725815</v>
       </c>
       <c r="D5" t="n">
-        <v>39.63806355896497</v>
+        <v>48.62105505282329</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.74347041621788</v>
+        <v>10.18366893615217</v>
       </c>
       <c r="C6" t="n">
-        <v>178.7978553928376</v>
+        <v>140.8807955594173</v>
       </c>
       <c r="D6" t="n">
-        <v>36.74976181307086</v>
+        <v>28.94094057349173</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.97271635292611</v>
+        <v>5.629341336151211</v>
       </c>
       <c r="C7" t="n">
-        <v>170.0779722837174</v>
+        <v>65.27640485537042</v>
       </c>
       <c r="D7" t="n">
-        <v>37.36924461445059</v>
+        <v>28.68568617038755</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.93452600345173</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>110.485886635936</v>
+        <v>31.2097595180061</v>
       </c>
       <c r="D8" t="n">
-        <v>35.46563581591602</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>55.02499532762521</v>
+        <v>29.28749751309084</v>
       </c>
       <c r="D9" t="n">
-        <v>34.50155957034565</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>3.274128593663113</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>29.04009709162065</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>37.43894870145212</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>37.13853390395258</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>22.78145547704723</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>37.31819373382975</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>35.12202411942965</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>27.04125876577415</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>10.70104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>83.65177663575797</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.677555772604489</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93.09036374282942</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.63725024418005</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.667228585989336</v>
+        <v>1.807397523518378</v>
       </c>
       <c r="C2" t="n">
-        <v>14.0036492533765</v>
+        <v>6.17421131200819</v>
       </c>
       <c r="D2" t="n">
-        <v>33.15263822471054</v>
+        <v>12.48292205949819</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.28933783531232</v>
+        <v>7.69199326277376</v>
       </c>
       <c r="C3" t="n">
-        <v>32.73637719810989</v>
+        <v>29.84513020910304</v>
       </c>
       <c r="D3" t="n">
-        <v>53.15182070792231</v>
+        <v>62.87112297996573</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.98039040811084</v>
+        <v>19.60353815840031</v>
       </c>
       <c r="C4" t="n">
-        <v>57.63644422092175</v>
+        <v>147.128637949244</v>
       </c>
       <c r="D4" t="n">
-        <v>56.58990116819465</v>
+        <v>94.27821378652546</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.34983064454391</v>
+        <v>20.93576979306323</v>
       </c>
       <c r="C5" t="n">
-        <v>115.3553552490002</v>
+        <v>263.7710644385118</v>
       </c>
       <c r="D5" t="n">
-        <v>45.89670517353839</v>
+        <v>65.13896017677588</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.98876847355934</v>
+        <v>14.93336432929824</v>
       </c>
       <c r="C6" t="n">
-        <v>183.7488090653543</v>
+        <v>233.8218689727586</v>
       </c>
       <c r="D6" t="n">
-        <v>40.57366912111219</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.93763547748049</v>
+        <v>8.26435217434965</v>
       </c>
       <c r="C7" t="n">
-        <v>212.2980323048515</v>
+        <v>128.0974587024196</v>
       </c>
       <c r="D7" t="n">
-        <v>39.16584291322225</v>
+        <v>30.3625112492411</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.27661617288612</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>162.6412334240478</v>
+        <v>55.49328898255096</v>
       </c>
       <c r="D8" t="n">
-        <v>37.46840113257952</v>
+        <v>31.12631096314512</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.873436661610169</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>92.74374212478766</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.978843518863076</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>47.11898106532567</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>37.72365553568369</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>37.84931924182727</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.8092064546734</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>21.853703896534</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>27.9631198600619</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>24.72531593145592</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>24.38563122578652</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.52772260099505</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>43.93222801734051</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.855354287319452</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>101.1376864492379</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.819192859149315</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.10647072041516</v>
+        <v>1.029853341754904</v>
       </c>
       <c r="C2" t="n">
-        <v>16.56993775227766</v>
+        <v>2.906954952274805</v>
       </c>
       <c r="D2" t="n">
-        <v>25.94857357094745</v>
+        <v>8.615817852470007</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.5740446695439</v>
+        <v>7.731263170943632</v>
       </c>
       <c r="C3" t="n">
-        <v>42.49004063980195</v>
+        <v>29.24135537099124</v>
       </c>
       <c r="D3" t="n">
-        <v>63.25891332314323</v>
+        <v>61.3101441302133</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.41883072128167</v>
+        <v>21.09677641655971</v>
       </c>
       <c r="C4" t="n">
-        <v>68.30607827067608</v>
+        <v>136.2420376568511</v>
       </c>
       <c r="D4" t="n">
-        <v>66.07260224351459</v>
+        <v>103.799203022311</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.12893741108838</v>
+        <v>20.17491532227196</v>
       </c>
       <c r="C5" t="n">
-        <v>109.980286568249</v>
+        <v>304.7590310908162</v>
       </c>
       <c r="D5" t="n">
-        <v>53.55433726666352</v>
+        <v>69.53228115328035</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.57745724320893</v>
+        <v>11.18996033300515</v>
       </c>
       <c r="C6" t="n">
-        <v>182.5010077332566</v>
+        <v>269.5653393889765</v>
       </c>
       <c r="D6" t="n">
-        <v>44.27682146153116</v>
+        <v>36.91076843656734</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.48334833232147</v>
+        <v>4.012402867256713</v>
       </c>
       <c r="C7" t="n">
-        <v>236.7317691681461</v>
+        <v>112.2873936732289</v>
       </c>
       <c r="D7" t="n">
-        <v>41.62119392154352</v>
+        <v>31.91956310817654</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>26.20284622634736</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>211.8758807920254</v>
+        <v>41.8911745402114</v>
       </c>
       <c r="D8" t="n">
-        <v>38.88702656521616</v>
+        <v>35.21529015133309</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.64531134132641</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>137.6734258096429</v>
+        <v>24.73906039931537</v>
       </c>
       <c r="D9" t="n">
-        <v>36.94218436310322</v>
+        <v>39.160934174701</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.402377690020952</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>73.027302980399</v>
+        <v>25.48126166372597</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>29.60951076008381</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>41.75863860013807</v>
+        <v>21.32356013624072</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>23.15451960466103</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>20.58823110575986</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.05273663858884</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>37.98872741583033</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.016687329057383</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109.2273648584068</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.0229450774539</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.536075304247763</v>
+        <v>0.6695519342963246</v>
       </c>
       <c r="C2" t="n">
-        <v>11.40005434171396</v>
+        <v>8.714974370598936</v>
       </c>
       <c r="D2" t="n">
-        <v>21.36577528752333</v>
+        <v>8.767006998924016</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.84326452468578</v>
+        <v>5.703954161673969</v>
       </c>
       <c r="C3" t="n">
-        <v>60.91253630999335</v>
+        <v>20.12582793705961</v>
       </c>
       <c r="D3" t="n">
-        <v>65.49729808882596</v>
+        <v>55.2969394417016</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.27170743436488</v>
+        <v>18.17411350101695</v>
       </c>
       <c r="C4" t="n">
-        <v>92.2744667221577</v>
+        <v>105.0754750378319</v>
       </c>
       <c r="D4" t="n">
-        <v>62.37141339850411</v>
+        <v>109.1723082076538</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.80171232593793</v>
+        <v>25.30454707696154</v>
       </c>
       <c r="C5" t="n">
-        <v>109.0476262492145</v>
+        <v>282.0315717375025</v>
       </c>
       <c r="D5" t="n">
-        <v>40.84070449666732</v>
+        <v>86.14836104765762</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.1170332654504</v>
+        <v>16.98619877887832</v>
       </c>
       <c r="C6" t="n">
-        <v>155.8946632004638</v>
+        <v>369.5907042361628</v>
       </c>
       <c r="D6" t="n">
-        <v>27.4113776502752</v>
+        <v>46.77242412572655</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.36711688812607</v>
+        <v>7.066619975168541</v>
       </c>
       <c r="C7" t="n">
-        <v>148.9978855781299</v>
+        <v>227.6290044543697</v>
       </c>
       <c r="D7" t="n">
-        <v>27.30829414132927</v>
+        <v>34.7941203862112</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.429686699290613</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>101.4734427109503</v>
+        <v>83.11476064153496</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>55.69062027110455</v>
+        <v>35.05624702324509</v>
       </c>
       <c r="D9" t="n">
-        <v>27.40156017323271</v>
+        <v>39.71562162760046</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.558835427894688</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>28.04362317181014</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>31.17539834835747</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>26.4698816019025</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>23.15451960466103</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
+        <v>20.89551813718911</v>
+      </c>
+      <c r="D14" t="n">
         <v>20.28094407433061</v>
-      </c>
-      <c r="D14" t="n">
-        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>38.02505208088746</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>45.80540263704344</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.387029579651496</v>
+        <v>0.3711006322052943</v>
       </c>
       <c r="C2" t="n">
-        <v>4.902848035008571</v>
+        <v>4.653484118129881</v>
       </c>
       <c r="D2" t="n">
-        <v>15.00306841629976</v>
+        <v>6.802529842726149</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.88882582970863</v>
+        <v>4.334416114249668</v>
       </c>
       <c r="C3" t="n">
-        <v>53.66232951413066</v>
+        <v>26.89006961932013</v>
       </c>
       <c r="D3" t="n">
-        <v>67.97130230352791</v>
+        <v>50.90852720371836</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.90832191507333</v>
+        <v>15.86406115292421</v>
       </c>
       <c r="C4" t="n">
-        <v>124.3471824721968</v>
+        <v>84.64236006934301</v>
       </c>
       <c r="D4" t="n">
-        <v>76.61460909171683</v>
+        <v>112.5927172092497</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.10881943091793</v>
+        <v>26.87534340375644</v>
       </c>
       <c r="C5" t="n">
-        <v>139.5799798512903</v>
+        <v>255.867995419325</v>
       </c>
       <c r="D5" t="n">
-        <v>50.24093876483053</v>
+        <v>97.41391595388978</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.74597369097411</v>
+        <v>21.01136436629024</v>
       </c>
       <c r="C6" t="n">
-        <v>171.5928089913703</v>
+        <v>417.3291681028682</v>
       </c>
       <c r="D6" t="n">
-        <v>31.67805317293184</v>
+        <v>55.74854338565514</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.22927129890402</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>183.9716657942183</v>
+        <v>318.8961980319702</v>
       </c>
       <c r="D7" t="n">
-        <v>29.88341836956866</v>
+        <v>37.90822410408209</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.011061266653972</v>
+        <v>3.922082078466008</v>
       </c>
       <c r="C8" t="n">
-        <v>132.2659594546515</v>
+        <v>126.0907663949391</v>
       </c>
       <c r="D8" t="n">
-        <v>27.95526587842792</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.326562132615692</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>61.34843229067891</v>
+        <v>41.82343394861835</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>39.2718716652809</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>34.44952694202058</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>32.45657910239955</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>25.23287949455151</v>
       </c>
       <c r="D11" t="n">
-        <v>29.14219885286231</v>
+        <v>32.16303653882975</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>27.98864530037232</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>23.41468274628643</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>15.97892563432109</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>39.26499943135118</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.374266859496287</v>
+        <v>0.8374307917225292</v>
       </c>
       <c r="C2" t="n">
-        <v>10.42517887139688</v>
+        <v>12.72050500392592</v>
       </c>
       <c r="D2" t="n">
-        <v>16.17822041828319</v>
+        <v>14.2215972437193</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.18272824617692</v>
+        <v>2.910881943091793</v>
       </c>
       <c r="C3" t="n">
-        <v>35.75525138866883</v>
+        <v>22.64401079845268</v>
       </c>
       <c r="D3" t="n">
-        <v>64.35847075189966</v>
+        <v>45.62181581634928</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.83473189498382</v>
+        <v>12.50746575210436</v>
       </c>
       <c r="C4" t="n">
-        <v>129.0438634893135</v>
+        <v>76.65289725218247</v>
       </c>
       <c r="D4" t="n">
-        <v>90.61531310198059</v>
+        <v>112.0056320821101</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.60031517784709</v>
+        <v>25.69724615866027</v>
       </c>
       <c r="C5" t="n">
-        <v>182.5314419120882</v>
+        <v>212.9901644363456</v>
       </c>
       <c r="D5" t="n">
-        <v>63.61725123519332</v>
+        <v>110.4466167277662</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.09315252537899</v>
+        <v>26.56609287691869</v>
       </c>
       <c r="C6" t="n">
-        <v>196.9111005361913</v>
+        <v>414.6725588151763</v>
       </c>
       <c r="D6" t="n">
-        <v>38.56108632740622</v>
+        <v>67.98504677138737</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.83487076370406</v>
+        <v>12.75584792127881</v>
       </c>
       <c r="C7" t="n">
-        <v>213.914970773746</v>
+        <v>434.3575820330291</v>
       </c>
       <c r="D7" t="n">
-        <v>31.91956310817654</v>
+        <v>42.75903951076558</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.43245201595411</v>
+        <v>5.006913291658733</v>
       </c>
       <c r="C8" t="n">
-        <v>183.3364750295706</v>
+        <v>236.4097559211531</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>38.88702656521616</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>105.0578035791554</v>
+        <v>81.20624310447914</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>39.82655911818034</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>49.39663573917827</v>
+        <v>37.29659528433633</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>34.29539255245382</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.69612554223576</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2495,7 +2495,7 @@
         <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
+        <v>19.66637001147211</v>
+      </c>
+      <c r="D14" t="n">
         <v>16.28621266575034</v>
-      </c>
-      <c r="D14" t="n">
-        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>34.04210164475815</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>9.675123625352315</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.009637550593221</v>
+        <v>0.6027930904075416</v>
       </c>
       <c r="C2" t="n">
-        <v>4.948990177108171</v>
+        <v>7.326783116793946</v>
       </c>
       <c r="D2" t="n">
-        <v>11.28813510342983</v>
+        <v>10.58127675637212</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.03055735201867</v>
+        <v>4.368777283898306</v>
       </c>
       <c r="C3" t="n">
-        <v>40.09457624143974</v>
+        <v>33.81139093426015</v>
       </c>
       <c r="D3" t="n">
-        <v>64.63336010908876</v>
+        <v>50.67290775469912</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.02541193378595</v>
+        <v>18.69738502738051</v>
       </c>
       <c r="C4" t="n">
-        <v>127.3081335482051</v>
+        <v>114.3156844302029</v>
       </c>
       <c r="D4" t="n">
-        <v>99.15357288581511</v>
+        <v>113.7796501836841</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.46563581591603</v>
+        <v>15.4379826492811</v>
       </c>
       <c r="C5" t="n">
-        <v>226.464651677133</v>
+        <v>337.6966665682966</v>
       </c>
       <c r="D5" t="n">
-        <v>68.01057221169781</v>
+        <v>99.81919782929447</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.33716573537994</v>
+        <v>7.889324551327369</v>
       </c>
       <c r="C6" t="n">
-        <v>237.4445180014294</v>
+        <v>363.3114459198002</v>
       </c>
       <c r="D6" t="n">
-        <v>38.88309957439917</v>
+        <v>57.80137783523521</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.545712854840985</v>
+        <v>3.293763547748049</v>
       </c>
       <c r="C7" t="n">
-        <v>230.6832215622815</v>
+        <v>166.2452292463379</v>
       </c>
       <c r="D7" t="n">
-        <v>32.5184292077671</v>
+        <v>32.75797564760332</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.838633523605028</v>
+        <v>1.919316761802514</v>
       </c>
       <c r="C8" t="n">
-        <v>131.2645767963198</v>
+        <v>59.83261383532185</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.9984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>37.71874679716245</v>
+        <v>28.39999758845172</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>25.62656032395449</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>22.20713307006285</v>
       </c>
       <c r="D10" t="n">
-        <v>23.20360698987336</v>
+        <v>25.62361508084176</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.72429312602266</v>
+        <v>18.8358114536793</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>22.92282714645877</v>
       </c>
     </row>
     <row r="12">
@@ -2792,7 +2792,7 @@
         <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>19.52696183746906</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
+        <v>16.1301147807751</v>
+      </c>
+      <c r="D13" t="n">
         <v>13.26832022289564</v>
-      </c>
-      <c r="D13" t="n">
-        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>7.989462817160544</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.52996383384403</v>
+        <v>0.2955060589782899</v>
       </c>
       <c r="C2" t="n">
-        <v>11.98321247803657</v>
+        <v>4.91561075516378</v>
       </c>
       <c r="D2" t="n">
-        <v>9.315803965597985</v>
+        <v>7.955101647511905</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.15265392024377</v>
+        <v>3.244676162535709</v>
       </c>
       <c r="C3" t="n">
-        <v>29.71259426902972</v>
+        <v>31.11158474758142</v>
       </c>
       <c r="D3" t="n">
-        <v>59.79334392715199</v>
+        <v>47.47241023885451</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.48563062289946</v>
+        <v>12.91587279707104</v>
       </c>
       <c r="C4" t="n">
-        <v>114.0221418666331</v>
+        <v>96.53721525399736</v>
       </c>
       <c r="D4" t="n">
-        <v>106.7091032176986</v>
+        <v>108.3554941177205</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.11697651218817</v>
+        <v>15.95340019401067</v>
       </c>
       <c r="C5" t="n">
-        <v>232.0115262061275</v>
+        <v>252.0146356801563</v>
       </c>
       <c r="D5" t="n">
-        <v>83.59581701661591</v>
+        <v>102.2735670899115</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.02523200733671</v>
+        <v>7.84907289545325</v>
       </c>
       <c r="C6" t="n">
-        <v>292.9112997959657</v>
+        <v>360.3730750409895</v>
       </c>
       <c r="D6" t="n">
-        <v>48.1409804254466</v>
+        <v>60.21647718768238</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.63040519931347</v>
+        <v>2.515237618280328</v>
       </c>
       <c r="C7" t="n">
-        <v>283.1438918864141</v>
+        <v>218.0471468609208</v>
       </c>
       <c r="D7" t="n">
-        <v>35.69241953559704</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.090361846519712</v>
+        <v>0.9179341034707675</v>
       </c>
       <c r="C8" t="n">
-        <v>200.8606715503762</v>
+        <v>72.76713983877357</v>
       </c>
       <c r="D8" t="n">
-        <v>32.71183350550372</v>
+        <v>25.11801501315464</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>81.6499930667987</v>
+        <v>26.40312275801371</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>15.23181563138926</v>
       </c>
       <c r="D10" t="n">
-        <v>24.48478774391545</v>
+        <v>19.3600647277471</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>12.08335074386974</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>16.70345544005523</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>12.80100831567416</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>7.804894248762142</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.458296251434013</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.644427404613408</v>
+        <v>0.3082687791334984</v>
       </c>
       <c r="C2" t="n">
-        <v>6.856525966459724</v>
+        <v>18.7896693115797</v>
       </c>
       <c r="D2" t="n">
-        <v>8.179921871784424</v>
+        <v>8.839656329038281</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.18563243156066</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C3" t="n">
-        <v>37.43894870145211</v>
+        <v>24.65168485363741</v>
       </c>
       <c r="D3" t="n">
-        <v>55.15458602458581</v>
+        <v>43.09381547791374</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.34600146471816</v>
+        <v>9.648616437337653</v>
       </c>
       <c r="C4" t="n">
-        <v>100.4553703416464</v>
+        <v>86.55676809262428</v>
       </c>
       <c r="D4" t="n">
-        <v>110.5634447045715</v>
+        <v>107.653544509184</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.0622196249286</v>
+        <v>17.79417713947344</v>
       </c>
       <c r="C5" t="n">
-        <v>229.4589821750858</v>
+        <v>214.2664364518664</v>
       </c>
       <c r="D5" t="n">
-        <v>95.49950793060849</v>
+        <v>116.4598214162779</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.78121879733577</v>
+        <v>13.8063179648229</v>
       </c>
       <c r="C6" t="n">
-        <v>331.3918828116236</v>
+        <v>385.0875917476987</v>
       </c>
       <c r="D6" t="n">
-        <v>55.34602682691394</v>
+        <v>75.91462297858888</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.07335334037803</v>
+        <v>5.449681506274044</v>
       </c>
       <c r="C7" t="n">
-        <v>338.2994596587041</v>
+        <v>361.3558044929405</v>
       </c>
       <c r="D7" t="n">
-        <v>38.80652325346792</v>
+        <v>39.40538935305847</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>250.5125616926586</v>
+        <v>173.0723027816702</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>91.52342972840887</v>
+        <v>54.80312034646543</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>21.52187317249857</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>22.20713307006285</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>19.78712497909446</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>14.57109942643116</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>17.41424077792992</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.70640068316797</v>
+        <v>12.15010958775853</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>15.67163860289184</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.443570035870311</v>
+        <v>0.5330890034060181</v>
       </c>
       <c r="C2" t="n">
-        <v>20.469439633546</v>
+        <v>18.79457805010094</v>
       </c>
       <c r="D2" t="n">
-        <v>13.13774777823082</v>
+        <v>12.22374066557704</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.025787482217675</v>
+        <v>1.546252634188726</v>
       </c>
       <c r="C3" t="n">
-        <v>32.63820242768521</v>
+        <v>48.38052686528282</v>
       </c>
       <c r="D3" t="n">
-        <v>50.44219704420112</v>
+        <v>40.40382676827748</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.0832529328785</v>
+        <v>6.917394324123026</v>
       </c>
       <c r="C4" t="n">
-        <v>96.14157092918589</v>
+        <v>74.39389578471055</v>
       </c>
       <c r="D4" t="n">
-        <v>110.5506819844163</v>
+        <v>104.0161692649496</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.00684084286328</v>
+        <v>16.51790512395259</v>
       </c>
       <c r="C5" t="n">
-        <v>210.3885330200915</v>
+        <v>188.691908756237</v>
       </c>
       <c r="D5" t="n">
-        <v>108.3358591636355</v>
+        <v>126.8172596960817</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.66425195181016</v>
+        <v>17.99249017573129</v>
       </c>
       <c r="C6" t="n">
-        <v>345.4799623675653</v>
+        <v>363.5127041991708</v>
       </c>
       <c r="D6" t="n">
-        <v>67.26051696565324</v>
+        <v>91.4517621459989</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.33203601268044</v>
+        <v>10.00106386316226</v>
       </c>
       <c r="C7" t="n">
-        <v>397.587203518169</v>
+        <v>450.3473068920968</v>
       </c>
       <c r="D7" t="n">
-        <v>43.47767883027424</v>
+        <v>48.68781389671206</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.34347282776614</v>
+        <v>3.254493639578176</v>
       </c>
       <c r="C8" t="n">
-        <v>323.94728997032</v>
+        <v>305.7555050106266</v>
       </c>
       <c r="D8" t="n">
-        <v>35.71598148049896</v>
+        <v>30.79251674370121</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>0.8874999246391163</v>
       </c>
       <c r="C9" t="n">
-        <v>168.0702982285327</v>
+        <v>121.6984271661388</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>23.07499804061703</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>57.51078051477815</v>
+        <v>39.28954312395736</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>20.21418523044183</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.25371718051895</v>
+        <v>19.19120412261664</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>17.94732978133594</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.30999559483051</v>
+        <v>13.88583952886689</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.380157345721768</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>6.808420328951629</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>0.4133157834879072</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.547455366071226</v>
+        <v>4.702571503342222</v>
       </c>
       <c r="C2" t="n">
-        <v>12.12949288596934</v>
+        <v>25.03260296288517</v>
       </c>
       <c r="D2" t="n">
-        <v>5.273948667213865</v>
+        <v>8.135743225093318</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.783835578616454</v>
+        <v>0.6891868883812609</v>
       </c>
       <c r="C2" t="n">
-        <v>12.11869366122263</v>
+        <v>26.66721289045611</v>
       </c>
       <c r="D2" t="n">
-        <v>9.774280143481244</v>
+        <v>18.52754267454581</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.79431600819368</v>
+        <v>1.600248757922301</v>
       </c>
       <c r="C3" t="n">
-        <v>50.46674073680729</v>
+        <v>58.5121631731099</v>
       </c>
       <c r="D3" t="n">
-        <v>55.36566178099887</v>
+        <v>40.20256848890688</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.43832680664636</v>
+        <v>5.079562621772998</v>
       </c>
       <c r="C4" t="n">
-        <v>134.64669763745</v>
+        <v>92.84878912914209</v>
       </c>
       <c r="D4" t="n">
-        <v>111.1505298317111</v>
+        <v>99.98314969590368</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.80800372279091</v>
+        <v>14.21079801897258</v>
       </c>
       <c r="C5" t="n">
-        <v>300.562059655161</v>
+        <v>166.7989349515331</v>
       </c>
       <c r="D5" t="n">
-        <v>98.49383842856128</v>
+        <v>132.7813769993811</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.6981457909065</v>
+        <v>19.44154978719959</v>
       </c>
       <c r="C6" t="n">
-        <v>322.8182801104363</v>
+        <v>336.7051013870074</v>
       </c>
       <c r="D6" t="n">
-        <v>57.47936458824226</v>
+        <v>103.8895238111017</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.850815406683489</v>
+        <v>14.13323995033708</v>
       </c>
       <c r="C7" t="n">
-        <v>227.8086642842468</v>
+        <v>483.8239218592088</v>
       </c>
       <c r="D7" t="n">
-        <v>30.18285141936394</v>
+        <v>59.28774385946488</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.50207398749762</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>123.8376554136927</v>
+        <v>416.1579430917017</v>
       </c>
       <c r="D8" t="n">
-        <v>24.11663235482289</v>
+        <v>34.46425315758427</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>43.82030877905637</v>
+        <v>219.3234188764416</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>24.84999788989526</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>22.06477965294707</v>
+        <v>76.58613840829368</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>20.78359889890498</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.45958109877452</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>14.53673825678252</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>9.675123625352315</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.932701376763475</v>
+        <v>4.894994053374596</v>
       </c>
       <c r="C2" t="n">
-        <v>8.604036880019047</v>
+        <v>17.84817326320701</v>
       </c>
       <c r="D2" t="n">
-        <v>6.361725123519331</v>
+        <v>33.44421729287184</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.665306148309849</v>
+        <v>7.584001015306611</v>
       </c>
       <c r="C3" t="n">
-        <v>30.56180603320321</v>
+        <v>49.42608817030567</v>
       </c>
       <c r="D3" t="n">
-        <v>7.564366061221674</v>
+        <v>8.595201150680825</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.657010198319369</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.675483478250811</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39823357613089</v>
+        <v>11.67646451420035</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14369342797936</v>
+        <v>59.93918450622848</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576262773662457</v>
+        <v>0.7784309676133568</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.826852551154067</v>
+        <v>3.206388002070083</v>
       </c>
       <c r="C2" t="n">
-        <v>10.004009106275</v>
+        <v>9.129271901791089</v>
       </c>
       <c r="D2" t="n">
-        <v>7.677267047210058</v>
+        <v>23.84566998845078</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.13502351929633</v>
+        <v>13.41067364001143</v>
       </c>
       <c r="C3" t="n">
-        <v>32.43203540979338</v>
+        <v>63.24418710757953</v>
       </c>
       <c r="D3" t="n">
-        <v>11.07902284242526</v>
+        <v>34.6115153132213</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.34605821798039</v>
+        <v>9.278497552836605</v>
       </c>
       <c r="C4" t="n">
-        <v>47.0944373727195</v>
+        <v>78.3503390328252</v>
       </c>
       <c r="D4" t="n">
-        <v>19.02921575141593</v>
+        <v>18.49318150489717</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.478912953223197</v>
       </c>
       <c r="C5" t="n">
-        <v>5.424156065963628</v>
+        <v>5.178719139901926</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.433973543006096</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.3497485290859</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.06307819944583</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>6.989061906533041</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>44.84132639147307</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.58545009356315</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44140598968469</v>
+        <v>13.61820534284413</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14679131087247</v>
+        <v>73.69852303186235</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250822313617829</v>
+        <v>1.602141805040486</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.301437602932777</v>
+        <v>2.946224860444678</v>
       </c>
       <c r="C2" t="n">
-        <v>10.12672756930585</v>
+        <v>8.827875356587318</v>
       </c>
       <c r="D2" t="n">
-        <v>12.76664714602552</v>
+        <v>25.4714441866835</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.51023106876786</v>
+        <v>12.12458414744811</v>
       </c>
       <c r="C3" t="n">
-        <v>36.37375244234433</v>
+        <v>46.19122948481242</v>
       </c>
       <c r="D3" t="n">
-        <v>14.64767574736241</v>
+        <v>45.65617698599792</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.62830283518473</v>
+        <v>18.95263943048468</v>
       </c>
       <c r="C4" t="n">
-        <v>67.19572161717294</v>
+        <v>126.2998786559437</v>
       </c>
       <c r="D4" t="n">
-        <v>20.31825048709199</v>
+        <v>31.47286790274425</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.25926350937917</v>
+        <v>8.492117641734911</v>
       </c>
       <c r="C5" t="n">
-        <v>51.88536616944394</v>
+        <v>86.07472996983911</v>
       </c>
       <c r="D5" t="n">
-        <v>29.30516897176729</v>
+        <v>26.8262560185441</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.11574841810989</v>
+        <v>10.74719211838983</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>32.08056973167303</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>6.886960145291375</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.78845088416398</v>
+        <v>32.09922293805371</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.42692138262712</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.61594102565702</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.85156047467625</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.60937189136354</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>43.98720588877834</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.77947628610551</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.8744848292392</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>40.84561323518855</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73422966254635</v>
+        <v>14.81104097429096</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0788009415327</v>
+        <v>87.2205746263801</v>
       </c>
       <c r="D21" t="n">
-        <v>5.020268898763906</v>
+        <v>2.468506829048494</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.417864669110647</v>
+        <v>2.796999209399163</v>
       </c>
       <c r="C2" t="n">
-        <v>6.222316949516284</v>
+        <v>14.46310717896401</v>
       </c>
       <c r="D2" t="n">
-        <v>10.80904222375738</v>
+        <v>23.34596040698915</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.42954783057037</v>
+        <v>11.01030050312798</v>
       </c>
       <c r="C3" t="n">
-        <v>38.04763227808514</v>
+        <v>39.28463438543612</v>
       </c>
       <c r="D3" t="n">
-        <v>21.08794068722149</v>
+        <v>54.86006171331176</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.38505038870978</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="C4" t="n">
-        <v>80.50723873905544</v>
+        <v>120.3269256233061</v>
       </c>
       <c r="D4" t="n">
-        <v>22.93460811890974</v>
+        <v>46.41801320449344</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.06477965294707</v>
+        <v>18.43231314723387</v>
       </c>
       <c r="C5" t="n">
-        <v>90.88529372064848</v>
+        <v>165.5717503212246</v>
       </c>
       <c r="D5" t="n">
-        <v>29.82058651649687</v>
+        <v>31.56318869153496</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.861655689159212</v>
+        <v>7.929576207201488</v>
       </c>
       <c r="C6" t="n">
-        <v>48.26173539306896</v>
+        <v>75.59260973159593</v>
       </c>
       <c r="D6" t="n">
-        <v>38.07806645691679</v>
+        <v>33.6906359666378</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.84620976779852</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>34.37491411649782</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>25.45180923259856</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>35.04839304161113</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>27.29062268265283</v>
       </c>
       <c r="D9" t="n">
-        <v>42.26718391093791</v>
+        <v>37.60780930658255</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>43.41779222031519</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>27.8983245115816</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>28.42257778564941</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>43.17628228507047</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.11939767148639</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05625894831553</v>
+        <v>16.02369063409634</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7955940913918</v>
+        <v>100.3589044977613</v>
       </c>
       <c r="D21" t="n">
-        <v>6.878574837453537</v>
+        <v>3.373408554546599</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.684900044665779</v>
+        <v>2.427862072602362</v>
       </c>
       <c r="C2" t="n">
-        <v>5.115887286830128</v>
+        <v>11.82220585454009</v>
       </c>
       <c r="D2" t="n">
-        <v>17.19727453529138</v>
+        <v>22.69015294055228</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.96536109291088</v>
+        <v>10.15618000043325</v>
       </c>
       <c r="C3" t="n">
-        <v>28.34305622160542</v>
+        <v>48.18417732443346</v>
       </c>
       <c r="D3" t="n">
-        <v>23.15451960466102</v>
+        <v>59.99460220652258</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.10953913671491</v>
+        <v>21.09677641655971</v>
       </c>
       <c r="C4" t="n">
-        <v>73.41116633275949</v>
+        <v>108.7383757223767</v>
       </c>
       <c r="D4" t="n">
-        <v>24.45337181737955</v>
+        <v>61.63117562950202</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18.33413837680919</v>
+        <v>24.98547907308133</v>
       </c>
       <c r="C5" t="n">
-        <v>90.56622571676827</v>
+        <v>193.7233657405019</v>
       </c>
       <c r="D5" t="n">
-        <v>25.18182861393069</v>
+        <v>40.00621894805753</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.78744377426395</v>
+        <v>15.61764247915826</v>
       </c>
       <c r="C6" t="n">
-        <v>65.69070238656259</v>
+        <v>164.3475109340288</v>
       </c>
       <c r="D6" t="n">
-        <v>30.3497485290859</v>
+        <v>35.66296710446964</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.150248456478767</v>
+        <v>7.964919124554372</v>
       </c>
       <c r="C7" t="n">
-        <v>29.2845522699781</v>
+        <v>61.38377520803181</v>
       </c>
       <c r="D7" t="n">
-        <v>30.84160412891355</v>
+        <v>36.47094546506476</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.20837685967435</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.098436812331936</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>30.06405994715006</v>
+        <v>38.49530923122167</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.687084524252525</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>43.56014563743098</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>30.20837685967435</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>5.858088551240717</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>30.15830772675777</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>44.2611134982632</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>26.87534340375643</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.054933681079971</v>
+        <v>17.24838128725418</v>
       </c>
       <c r="C21" t="n">
-        <v>66.14000326012473</v>
+        <v>112.9768974315149</v>
       </c>
       <c r="D21" t="n">
-        <v>5.291200260809978</v>
+        <v>4.312095321813544</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.628940425523711</v>
+        <v>2.676244241776805</v>
       </c>
       <c r="C2" t="n">
-        <v>5.703954161673968</v>
+        <v>10.46935751808799</v>
       </c>
       <c r="D2" t="n">
-        <v>13.46565151144925</v>
+        <v>22.93264462350124</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.63924092865169</v>
+        <v>9.06153131019806</v>
       </c>
       <c r="C3" t="n">
-        <v>22.95817006381166</v>
+        <v>46.74100819919065</v>
       </c>
       <c r="D3" t="n">
-        <v>32.00497515844602</v>
+        <v>62.90057541109314</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.88730430265664</v>
+        <v>19.90984344212531</v>
       </c>
       <c r="C4" t="n">
-        <v>72.04555527615219</v>
+        <v>112.8862597728195</v>
       </c>
       <c r="D4" t="n">
-        <v>30.68157925312132</v>
+        <v>73.65365801570844</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.26175108860219</v>
+        <v>27.66074156715389</v>
       </c>
       <c r="C5" t="n">
-        <v>118.3005983617407</v>
+        <v>196.472259312393</v>
       </c>
       <c r="D5" t="n">
-        <v>28.81429511964389</v>
+        <v>50.82998738737862</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.75727163733956</v>
+        <v>23.38621206286328</v>
       </c>
       <c r="C6" t="n">
-        <v>111.7788483624291</v>
+        <v>225.9727960773054</v>
       </c>
       <c r="D6" t="n">
-        <v>32.00006641992479</v>
+        <v>39.48687441251096</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>12.33664165156542</v>
       </c>
       <c r="C7" t="n">
-        <v>67.19277637406019</v>
+        <v>138.5177288352952</v>
       </c>
       <c r="D7" t="n">
-        <v>32.87774886752143</v>
+        <v>37.96811071404115</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>8.094509821514951</v>
       </c>
       <c r="C8" t="n">
-        <v>30.70906818884022</v>
+        <v>49.06775025825559</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>37.80219535202343</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.098436812331936</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>31.06249736236907</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>38.93905919354123</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>43.84485247166256</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>32.32797015314322</v>
       </c>
       <c r="D12" t="n">
-        <v>32.76190263842031</v>
+        <v>45.12897846881738</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>31.47974013667398</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>28.30869505195678</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.275852294132944</v>
+        <v>17.59812800546979</v>
       </c>
       <c r="C21" t="n">
-        <v>75.48696755162931</v>
+        <v>124.9467088388355</v>
       </c>
       <c r="D21" t="n">
-        <v>6.366370757366326</v>
+        <v>5.279438401640936</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.225041208450772</v>
+        <v>2.511310627463341</v>
       </c>
       <c r="C2" t="n">
-        <v>5.960190312482386</v>
+        <v>7.035204048632643</v>
       </c>
       <c r="D2" t="n">
-        <v>21.92733497435251</v>
+        <v>18.64535239905542</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.86504290062846</v>
+        <v>12.38965602759475</v>
       </c>
       <c r="C3" t="n">
-        <v>22.49674864281566</v>
+        <v>68.65852569650069</v>
       </c>
       <c r="D3" t="n">
-        <v>35.34782609140641</v>
+        <v>67.31353134168255</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.20561154301086</v>
+        <v>13.28599168157209</v>
       </c>
       <c r="C4" t="n">
-        <v>63.5455836527833</v>
+        <v>162.0099696502171</v>
       </c>
       <c r="D4" t="n">
-        <v>39.83244960440584</v>
+        <v>66.80007729236148</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.25041208450773</v>
+        <v>13.15541923690726</v>
       </c>
       <c r="C5" t="n">
-        <v>126.9154344665064</v>
+        <v>135.0148530265426</v>
       </c>
       <c r="D5" t="n">
-        <v>33.15852871093603</v>
+        <v>37.7236555356837</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.97490083251287</v>
+        <v>7.647814616082655</v>
       </c>
       <c r="C6" t="n">
-        <v>153.9223320626319</v>
+        <v>91.21025221075418</v>
       </c>
       <c r="D6" t="n">
-        <v>34.29441080474959</v>
+        <v>24.99627829782805</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.40893112878119</v>
+        <v>5.329908286355933</v>
       </c>
       <c r="C7" t="n">
-        <v>117.9766216193392</v>
+        <v>34.49468733641593</v>
       </c>
       <c r="D7" t="n">
-        <v>35.09355343600648</v>
+        <v>26.52976821186155</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>62.75331325545612</v>
+        <v>22.86490403190821</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>28.62285431731576</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>31.8390597964283</v>
+        <v>25.29374785221481</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>25.48126166372597</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>25.9436648324262</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6518,10 +6518,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>33.84673385161303</v>
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>33.49428642578843</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.25041208450772</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>29.75873641112932</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>12.63803819676919</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>95.49459919208724</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.484031990776549</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.19535989623618</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.484031990776549</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
